--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -37074,7 +37074,7 @@
         <v>1065</v>
       </c>
       <c r="B789" t="n">
-        <v>2.18090909090909</v>
+        <v>2.179375</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -37134,7 +37134,7 @@
         <v>1066</v>
       </c>
       <c r="B790" t="n">
-        <v>2.195</v>
+        <v>2.20142857142857</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -2641,6 +2641,9 @@
     <t xml:space="preserve">Jan 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Feb 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">UnempRate</t>
   </si>
   <si>
@@ -3215,9 +3218,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 1968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Mar 2026</t>
@@ -18811,6 +18811,14 @@
         <v>21121.2</v>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="s">
+        <v>873</v>
+      </c>
+      <c r="B603" t="n">
+        <v>21037.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18828,7 +18836,7 @@
         <v>262</v>
       </c>
       <c r="B1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2">
@@ -23637,6 +23645,14 @@
       </c>
       <c r="B602" t="n">
         <v>6.5</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="s">
+        <v>873</v>
+      </c>
+      <c r="B603" t="n">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -23656,7 +23672,7 @@
         <v>262</v>
       </c>
       <c r="B1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2">
@@ -25261,7 +25277,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B202"/>
     </row>
@@ -25282,12 +25298,12 @@
         <v>262</v>
       </c>
       <c r="B1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B2" t="n">
         <v>12.9667760753128</v>
@@ -25295,7 +25311,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B3" t="n">
         <v>15.0136942094219</v>
@@ -25303,7 +25319,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B4" t="n">
         <v>15.7173673795166</v>
@@ -25311,7 +25327,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B5" t="n">
         <v>15.0083394292738</v>
@@ -25319,7 +25335,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B6" t="n">
         <v>14.1631513522075</v>
@@ -25327,7 +25343,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B7" t="n">
         <v>14.3196627658395</v>
@@ -25335,7 +25351,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B8" t="n">
         <v>14.5659126107761</v>
@@ -25343,7 +25359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B9" t="n">
         <v>11.0934019859703</v>
@@ -25351,7 +25367,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B10" t="n">
         <v>11.5193520347377</v>
@@ -25359,7 +25375,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B11" t="n">
         <v>10.3976063805748</v>
@@ -25367,7 +25383,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B12" t="n">
         <v>10.203544223433</v>
@@ -25375,7 +25391,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B13" t="n">
         <v>8.25370377873824</v>
@@ -25383,7 +25399,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B14" t="n">
         <v>6.74941660698323</v>
@@ -25391,7 +25407,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B15" t="n">
         <v>6.99352943674983</v>
@@ -25399,7 +25415,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B16" t="n">
         <v>8.54641293280502</v>
@@ -25407,7 +25423,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B17" t="n">
         <v>8.36923199167487</v>
@@ -25415,7 +25431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B18" t="n">
         <v>8.27326635899438</v>
@@ -25423,7 +25439,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B19" t="n">
         <v>9.85826112039194</v>
@@ -25431,7 +25447,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B20" t="n">
         <v>9.91121604952369</v>
@@ -25439,7 +25455,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B21" t="n">
         <v>10.5072207560502</v>
@@ -25447,7 +25463,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B22" t="n">
         <v>7.79066458038734</v>
@@ -25455,7 +25471,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B23" t="n">
         <v>10.9032596283834</v>
@@ -25463,7 +25479,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B24" t="n">
         <v>8.19610135662233</v>
@@ -25471,7 +25487,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B25" t="n">
         <v>9.07734774781358</v>
@@ -25479,7 +25495,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B26" t="n">
         <v>8.50235678691241</v>
@@ -25487,7 +25503,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B27" t="n">
         <v>9.00143117812621</v>
@@ -25495,7 +25511,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B28" t="n">
         <v>9.09344352882898</v>
@@ -25503,7 +25519,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B29" t="n">
         <v>8.12556120408371</v>
@@ -25511,7 +25527,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B30" t="n">
         <v>10.7444231936402</v>
@@ -25519,7 +25535,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B31" t="n">
         <v>10.0971199004294</v>
@@ -25527,7 +25543,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B32" t="n">
         <v>11.4278274718587</v>
@@ -25535,7 +25551,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B33" t="n">
         <v>12.506561942725</v>
@@ -25543,7 +25559,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B34" t="n">
         <v>14.8525484100527</v>
@@ -25551,7 +25567,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B35" t="n">
         <v>13.9647049646935</v>
@@ -25559,7 +25575,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B36" t="n">
         <v>13.8193035567392</v>
@@ -25567,7 +25583,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B37" t="n">
         <v>14.3299854004434</v>
@@ -25575,7 +25591,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B38" t="n">
         <v>15.3018079241173</v>
@@ -25583,7 +25599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B39" t="n">
         <v>15.0270385091154</v>
@@ -25591,7 +25607,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B40" t="n">
         <v>13.2518711756956</v>
@@ -25599,7 +25615,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B41" t="n">
         <v>13.1332186179338</v>
@@ -25607,7 +25623,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B42" t="n">
         <v>12.6578401751251</v>
@@ -25615,7 +25631,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B43" t="n">
         <v>11.2954913894953</v>
@@ -25623,7 +25639,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B44" t="n">
         <v>12.7456975920676</v>
@@ -25631,7 +25647,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B45" t="n">
         <v>12.0988566109835</v>
@@ -25639,7 +25655,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B46" t="n">
         <v>12.4954011343489</v>
@@ -25647,7 +25663,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B47" t="n">
         <v>14.2289904200083</v>
@@ -25655,7 +25671,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B48" t="n">
         <v>13.4484012949889</v>
@@ -25663,7 +25679,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B49" t="n">
         <v>15.6988273068042</v>
@@ -25671,7 +25687,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B50" t="n">
         <v>14.2845925451855</v>
@@ -25679,7 +25695,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B51" t="n">
         <v>13.7513624713095</v>
@@ -25687,7 +25703,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B52" t="n">
         <v>16.5561760195999</v>
@@ -25695,7 +25711,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B53" t="n">
         <v>15.9924726433944</v>
@@ -25703,7 +25719,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B54" t="n">
         <v>16.8425831874094</v>
@@ -25711,7 +25727,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B55" t="n">
         <v>16.5276746861153</v>
@@ -25719,7 +25735,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B56" t="n">
         <v>16.4698895002538</v>
@@ -25727,7 +25743,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B57" t="n">
         <v>17.2134250823613</v>
@@ -25735,7 +25751,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B58" t="n">
         <v>15.6816081666631</v>
@@ -25743,7 +25759,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B59" t="n">
         <v>14.8028853950233</v>
@@ -25751,7 +25767,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B60" t="n">
         <v>15.2426482221366</v>
@@ -25759,7 +25775,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B61" t="n">
         <v>15.6902851909184</v>
@@ -25767,7 +25783,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B62" t="n">
         <v>16.5013128950056</v>
@@ -25775,7 +25791,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B63" t="n">
         <v>17.144059922985</v>
@@ -25783,7 +25799,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B64" t="n">
         <v>17.3090733250565</v>
@@ -25791,7 +25807,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B65" t="n">
         <v>19.1915260629344</v>
@@ -25799,7 +25815,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B66" t="n">
         <v>22.7683604016704</v>
@@ -25807,7 +25823,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B67" t="n">
         <v>23.3483213053937</v>
@@ -25815,7 +25831,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B68" t="n">
         <v>23.7330017100268</v>
@@ -25823,7 +25839,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B69" t="n">
         <v>24.5746121277929</v>
@@ -25831,7 +25847,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B70" t="n">
         <v>25.299565253288</v>
@@ -25839,7 +25855,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B71" t="n">
         <v>25.0912717707172</v>
@@ -25847,7 +25863,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B72" t="n">
         <v>23.9521568788769</v>
@@ -25855,7 +25871,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B73" t="n">
         <v>21.1869735832747</v>
@@ -25863,7 +25879,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B74" t="n">
         <v>20.6527071997174</v>
@@ -25871,7 +25887,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B75" t="n">
         <v>20.1659943690496</v>
@@ -25879,7 +25895,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B76" t="n">
         <v>18.9358160000968</v>
@@ -25887,7 +25903,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B77" t="n">
         <v>16.9203967093089</v>
@@ -25895,7 +25911,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B78" t="n">
         <v>12.907810848208</v>
@@ -25903,7 +25919,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B79" t="n">
         <v>12.4545658937996</v>
@@ -25911,7 +25927,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B80" t="n">
         <v>13.2184526911685</v>
@@ -25919,7 +25935,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B81" t="n">
         <v>14.2594274489356</v>
@@ -25927,7 +25943,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B82" t="n">
         <v>14.1362614616155</v>
@@ -25935,7 +25951,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B83" t="n">
         <v>17.5108308988957</v>
@@ -25943,7 +25959,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B84" t="n">
         <v>17.8203047316368</v>
@@ -25951,7 +25967,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B85" t="n">
         <v>19.6199365813437</v>
@@ -25959,7 +25975,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B86" t="n">
         <v>18.3178769926645</v>
@@ -25967,7 +25983,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B87" t="n">
         <v>16.4922800191838</v>
@@ -25975,7 +25991,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B88" t="n">
         <v>18.0934981429238</v>
@@ -25983,7 +25999,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B89" t="n">
         <v>14.9717615097796</v>
@@ -25991,7 +26007,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B90" t="n">
         <v>15.137570465284</v>
@@ -25999,7 +26015,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B91" t="n">
         <v>17.0502997395172</v>
@@ -30819,15 +30835,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B2" t="n">
         <v>3.02666666666667</v>
@@ -30835,7 +30851,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B3" t="n">
         <v>2.66</v>
@@ -30843,7 +30859,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B4" t="n">
         <v>1.93285714285714</v>
@@ -30851,7 +30867,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B5" t="n">
         <v>2.59368421052632</v>
@@ -30859,7 +30875,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B6" t="n">
         <v>3.37809523809524</v>
@@ -30867,7 +30883,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B7" t="n">
         <v>3.61809523809524</v>
@@ -30875,7 +30891,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B8" t="n">
         <v>3.19952380952381</v>
@@ -30883,7 +30899,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B9" t="n">
         <v>3.0585</v>
@@ -30891,7 +30907,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B10" t="n">
         <v>3.20818181818182</v>
@@ -30899,7 +30915,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B11" t="n">
         <v>3.27578947368421</v>
@@ -30907,7 +30923,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B12" t="n">
         <v>3.18227272727273</v>
@@ -30915,7 +30931,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B13" t="n">
         <v>2.79714285714286</v>
@@ -30923,7 +30939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B14" t="n">
         <v>2.6</v>
@@ -30931,7 +30947,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B15" t="n">
         <v>2.4995652173913</v>
@@ -30939,7 +30955,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B16" t="n">
         <v>2.381</v>
@@ -30947,7 +30963,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B17" t="n">
         <v>2.52666666666667</v>
@@ -30955,7 +30971,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B18" t="n">
         <v>2.39909090909091</v>
@@ -30963,7 +30979,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B19" t="n">
         <v>2.73526315789474</v>
@@ -30971,7 +30987,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B20" t="n">
         <v>3.06681818181818</v>
@@ -30979,7 +30995,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B21" t="n">
         <v>3.0855</v>
@@ -30987,7 +31003,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B22" t="n">
         <v>3.10681818181818</v>
@@ -30995,7 +31011,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B23" t="n">
         <v>3.07421052631579</v>
@@ -31003,7 +31019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B24" t="n">
         <v>3.31772727272727</v>
@@ -31011,7 +31027,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B25" t="n">
         <v>4.24</v>
@@ -31019,7 +31035,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B26" t="n">
         <v>5.3725</v>
@@ -31027,7 +31043,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B27" t="n">
         <v>5.12</v>
@@ -31035,7 +31051,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B28" t="n">
         <v>5.01055555555556</v>
@@ -31043,7 +31059,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B29" t="n">
         <v>4.515</v>
@@ -31051,7 +31067,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B30" t="n">
         <v>3.85909090909091</v>
@@ -31059,7 +31075,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B31" t="n">
         <v>3.835</v>
@@ -31067,7 +31083,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B32" t="n">
         <v>3.83181818181818</v>
@@ -31075,7 +31091,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B33" t="n">
         <v>3.6535</v>
@@ -31083,7 +31099,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B34" t="n">
         <v>3.61904761904762</v>
@@ -31091,7 +31107,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B35" t="n">
         <v>3.5955</v>
@@ -31099,7 +31115,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B36" t="n">
         <v>3.37176470588235</v>
@@ -31107,7 +31123,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B37" t="n">
         <v>3.21842105263158</v>
@@ -31115,7 +31131,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B38" t="n">
         <v>3.37227272727273</v>
@@ -31123,7 +31139,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B39" t="n">
         <v>3.60190476190476</v>
@@ -31131,7 +31147,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B40" t="n">
         <v>3.688</v>
@@ -31139,7 +31155,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B41" t="n">
         <v>3.55136363636364</v>
@@ -31147,7 +31163,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B42" t="n">
         <v>3.622</v>
@@ -31155,7 +31171,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B43" t="n">
         <v>3.6925</v>
@@ -31163,7 +31179,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B44" t="n">
         <v>3.76</v>
@@ -31171,7 +31187,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B45" t="n">
         <v>3.7965</v>
@@ -31179,7 +31195,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B46" t="n">
         <v>3.8715</v>
@@ -31187,7 +31203,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B47" t="n">
         <v>3.74</v>
@@ -31195,7 +31211,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B48" t="n">
         <v>3.655</v>
@@ -31203,7 +31219,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B49" t="n">
         <v>3.54545454545455</v>
@@ -31211,7 +31227,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B50" t="n">
         <v>3.58952380952381</v>
@@ -31219,7 +31235,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B51" t="n">
         <v>3.78380952380952</v>
@@ -31227,7 +31243,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B52" t="n">
         <v>3.79809523809524</v>
@@ -31235,7 +31251,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B53" t="n">
         <v>3.69761904761905</v>
@@ -31243,7 +31259,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B54" t="n">
         <v>3.72315789473684</v>
@@ -31251,7 +31267,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B55" t="n">
         <v>3.84227272727273</v>
@@ -31259,7 +31275,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B56" t="n">
         <v>3.776</v>
@@ -31267,7 +31283,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B57" t="n">
         <v>3.7135</v>
@@ -31275,7 +31291,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B58" t="n">
         <v>3.7004347826087</v>
@@ -31283,7 +31299,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B59" t="n">
         <v>3.655</v>
@@ -31291,7 +31307,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B60" t="n">
         <v>3.8395</v>
@@ -31299,7 +31315,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B61" t="n">
         <v>3.95363636363636</v>
@@ -31307,7 +31323,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B62" t="n">
         <v>3.98190476190476</v>
@@ -31315,7 +31331,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B63" t="n">
         <v>4.08</v>
@@ -31323,7 +31339,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B64" t="n">
         <v>4.10428571428571</v>
@@ -31331,7 +31347,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B65" t="n">
         <v>4.1465</v>
@@ -31339,7 +31355,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B66" t="n">
         <v>4.17619047619048</v>
@@ -31347,7 +31363,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B67" t="n">
         <v>4.44045454545455</v>
@@ -31355,7 +31371,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B68" t="n">
         <v>4.59526315789474</v>
@@ -31363,7 +31379,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B69" t="n">
         <v>4.658</v>
@@ -31371,7 +31387,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B70" t="n">
         <v>4.84</v>
@@ -31379,7 +31395,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B71" t="n">
         <v>5.077</v>
@@ -31387,7 +31403,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B72" t="n">
         <v>5.08952380952381</v>
@@ -31395,7 +31411,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B73" t="n">
         <v>5.05090909090909</v>
@@ -31403,7 +31419,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B74" t="n">
         <v>5.06052631578947</v>
@@ -31411,7 +31427,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B75" t="n">
         <v>5.05</v>
@@ -31419,7 +31435,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B76" t="n">
         <v>5.01571428571429</v>
@@ -31427,7 +31443,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B77" t="n">
         <v>5.113</v>
@@ -31435,7 +31451,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B78" t="n">
         <v>5.19619047619048</v>
@@ -31443,7 +31459,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B79" t="n">
         <v>5.071</v>
@@ -31451,7 +31467,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B80" t="n">
         <v>4.82904761904762</v>
@@ -31459,7 +31475,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B81" t="n">
         <v>4.595</v>
@@ -31467,7 +31483,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B82" t="n">
         <v>4.27045454545455</v>
@@ -31475,7 +31491,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B83" t="n">
         <v>4.0045</v>
@@ -31483,7 +31499,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B84" t="n">
         <v>4.11954545454545</v>
@@ -31491,7 +31507,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B85" t="n">
         <v>4.33722222222222</v>
@@ -31499,7 +31515,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B86" t="n">
         <v>4.273</v>
@@ -31507,7 +31523,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B87" t="n">
         <v>4.32952380952381</v>
@@ -31515,7 +31531,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B88" t="n">
         <v>4.475</v>
@@ -31523,7 +31539,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B89" t="n">
         <v>4.90857142857143</v>
@@ -31531,7 +31547,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B90" t="n">
         <v>5.13904761904762</v>
@@ -31539,7 +31555,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B91" t="n">
         <v>5.753</v>
@@ -31547,7 +31563,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B92" t="n">
         <v>5.99181818181818</v>
@@ -31555,7 +31571,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B93" t="n">
         <v>6.60666666666667</v>
@@ -31563,7 +31579,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B94" t="n">
         <v>6.92285714285714</v>
@@ -31571,7 +31587,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B95" t="n">
         <v>6.91142857142857</v>
@@ -31579,7 +31595,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B96" t="n">
         <v>6.94714285714286</v>
@@ -31587,7 +31603,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B97" t="n">
         <v>6.7675</v>
@@ -31595,7 +31611,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B98" t="n">
         <v>6.23157894736842</v>
@@ -31603,7 +31619,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B99" t="n">
         <v>5.8</v>
@@ -31611,7 +31627,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B100" t="n">
         <v>5.59</v>
@@ -31619,7 +31635,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B101" t="n">
         <v>5.62636363636364</v>
@@ -31627,7 +31643,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B102" t="n">
         <v>5.6305</v>
@@ -31635,7 +31651,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B103" t="n">
         <v>5.898</v>
@@ -31643,7 +31659,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B104" t="n">
         <v>6.38272727272727</v>
@@ -31651,7 +31667,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B105" t="n">
         <v>6.28842105263158</v>
@@ -31659,7 +31675,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B106" t="n">
         <v>6.60571428571429</v>
@@ -31667,7 +31683,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B107" t="n">
         <v>6.67333333333333</v>
@@ -31675,7 +31691,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B108" t="n">
         <v>6.74571428571429</v>
@@ -31683,7 +31699,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B109" t="n">
         <v>6.9905</v>
@@ -31691,7 +31707,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B110" t="n">
         <v>7.44210526315789</v>
@@ -31699,7 +31715,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B111" t="n">
         <v>7.62666666666667</v>
@@ -31707,7 +31723,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B112" t="n">
         <v>7.73761904761905</v>
@@ -31715,7 +31731,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B113" t="n">
         <v>7.68363636363636</v>
@@ -31723,7 +31739,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B114" t="n">
         <v>7.69</v>
@@ -31731,7 +31747,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B115" t="n">
         <v>7.77117647058823</v>
@@ -31739,7 +31755,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B116" t="n">
         <v>7.80666666666667</v>
@@ -31747,7 +31763,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B117" t="n">
         <v>7.718125</v>
@@ -31755,7 +31771,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B118" t="n">
         <v>7.38857142857143</v>
@@ -31763,7 +31779,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B119" t="n">
         <v>6.80947368421053</v>
@@ -31771,7 +31787,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B120" t="n">
         <v>6.57315789473684</v>
@@ -31779,7 +31795,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B121" t="n">
         <v>5.92904761904762</v>
@@ -31787,7 +31803,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B122" t="n">
         <v>5.76611111111111</v>
@@ -31795,7 +31811,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B123" t="n">
         <v>5.676</v>
@@ -31803,7 +31819,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B124" t="n">
         <v>5.46285714285714</v>
@@ -31811,7 +31827,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B125" t="n">
         <v>5.30380952380952</v>
@@ -31819,7 +31835,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B126" t="n">
         <v>4.821875</v>
@@ -31827,7 +31843,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B127" t="n">
         <v>4.46105263157895</v>
@@ -31835,7 +31851,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B128" t="n">
         <v>4.583</v>
@@ -31843,7 +31859,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B129" t="n">
         <v>4.62421052631579</v>
@@ -31851,7 +31867,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B130" t="n">
         <v>3.36818181818182</v>
@@ -31859,7 +31875,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B131" t="n">
         <v>3.07333333333333</v>
@@ -31867,7 +31883,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B132" t="n">
         <v>3.0535</v>
@@ -31875,7 +31891,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B133" t="n">
         <v>3.10954545454545</v>
@@ -31883,7 +31899,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B134" t="n">
         <v>3.54142857142857</v>
@@ -31891,7 +31907,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B135" t="n">
         <v>3.87136363636364</v>
@@ -31899,7 +31915,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B136" t="n">
         <v>3.89666666666667</v>
@@ -31907,7 +31923,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B137" t="n">
         <v>3.848</v>
@@ -31915,7 +31931,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B138" t="n">
         <v>3.33285714285714</v>
@@ -31923,7 +31939,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B139" t="n">
         <v>3.24636363636364</v>
@@ -31931,7 +31947,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B140" t="n">
         <v>3.281</v>
@@ -31939,7 +31955,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B141" t="n">
         <v>3.47789473684211</v>
@@ -31947,7 +31963,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B142" t="n">
         <v>3.4952380952381</v>
@@ -31955,7 +31971,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B143" t="n">
         <v>3.64052631578947</v>
@@ -31963,7 +31979,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B144" t="n">
         <v>3.66952380952381</v>
@@ -31971,7 +31987,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B145" t="n">
         <v>3.61590909090909</v>
@@ -31979,7 +31995,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B146" t="n">
         <v>3.4875</v>
@@ -31987,7 +32003,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B147" t="n">
         <v>3.46</v>
@@ -31995,7 +32011,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B148" t="n">
         <v>3.5605</v>
@@ -32003,7 +32019,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B149" t="n">
         <v>3.56857142857143</v>
@@ -32011,7 +32027,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B150" t="n">
         <v>3.60571428571429</v>
@@ -32019,7 +32035,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B151" t="n">
         <v>3.67736842105263</v>
@@ -32027,7 +32043,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B152" t="n">
         <v>3.77727272727273</v>
@@ -32035,7 +32051,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B153" t="n">
         <v>3.925</v>
@@ -32043,7 +32059,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B154" t="n">
         <v>4.25636363636364</v>
@@ -32051,7 +32067,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B155" t="n">
         <v>4.71444444444444</v>
@@ -32059,7 +32075,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B156" t="n">
         <v>5.10681818181818</v>
@@ -32067,7 +32083,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B157" t="n">
         <v>5.35666666666667</v>
@@ -32075,7 +32091,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B158" t="n">
         <v>5.65285714285714</v>
@@ -32083,7 +32099,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B159" t="n">
         <v>6.01136363636364</v>
@@ -32091,7 +32107,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B160" t="n">
         <v>6.38105263157895</v>
@@ -32099,7 +32115,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B161" t="n">
         <v>6.48545454545455</v>
@@ -32107,7 +32123,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B162" t="n">
         <v>6.45952380952381</v>
@@ -32115,7 +32131,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B163" t="n">
         <v>6.38263157894737</v>
@@ -32123,7 +32139,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B164" t="n">
         <v>6.29090909090909</v>
@@ -32131,7 +32147,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B165" t="n">
         <v>6.1445</v>
@@ -32139,7 +32155,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B166" t="n">
         <v>6.25</v>
@@ -32147,7 +32163,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B167" t="n">
         <v>7.23571428571429</v>
@@ -32155,7 +32171,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B168" t="n">
         <v>8.28</v>
@@ -32163,7 +32179,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B169" t="n">
         <v>8.6555</v>
@@ -32171,7 +32187,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B170" t="n">
         <v>8.87954545454545</v>
@@ -32179,7 +32195,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B171" t="n">
         <v>9.09666666666667</v>
@@ -32187,7 +32203,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B172" t="n">
         <v>9.026</v>
@@ -32195,7 +32211,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B173" t="n">
         <v>8.63681818181818</v>
@@ -32203,7 +32219,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B174" t="n">
         <v>7.827</v>
@@ -32211,7 +32227,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B175" t="n">
         <v>7.3205</v>
@@ -32219,7 +32235,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B176" t="n">
         <v>6.65090909090909</v>
@@ -32227,7 +32243,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B177" t="n">
         <v>6.351</v>
@@ -32235,7 +32251,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B178" t="n">
         <v>6.277</v>
@@ -32243,7 +32259,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B179" t="n">
         <v>6.49181818181818</v>
@@ -32251,7 +32267,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B180" t="n">
         <v>6.92142857142857</v>
@@ -32259,7 +32275,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B181" t="n">
         <v>6.95285714285714</v>
@@ -32267,7 +32283,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B182" t="n">
         <v>7.22409090909091</v>
@@ -32275,7 +32291,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B183" t="n">
         <v>7.71125</v>
@@ -32283,7 +32299,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B184" t="n">
         <v>8.38380952380952</v>
@@ -32291,7 +32307,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B185" t="n">
         <v>8.32136363636364</v>
@@ -32299,7 +32315,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B186" t="n">
         <v>8.42105263157895</v>
@@ -32307,7 +32323,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B187" t="n">
         <v>8.55809523809524</v>
@@ -37123,7 +37139,7 @@
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1065</v>
+        <v>873</v>
       </c>
       <c r="B789" t="n">
         <v>2.18</v>
@@ -37134,7 +37150,7 @@
         <v>1066</v>
       </c>
       <c r="B790" t="n">
-        <v>2.20142857142857</v>
+        <v>2.21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -30250,7 +30250,7 @@
         <v>800</v>
       </c>
       <c r="B620" t="n">
-        <v>7.90427270958251</v>
+        <v>7.9032761475169</v>
       </c>
     </row>
     <row r="621">
@@ -30258,7 +30258,7 @@
         <v>801</v>
       </c>
       <c r="B621" t="n">
-        <v>7.66676567294967</v>
+        <v>7.69138081430181</v>
       </c>
     </row>
     <row r="622">
@@ -30266,7 +30266,7 @@
         <v>802</v>
       </c>
       <c r="B622" t="n">
-        <v>11.0628186335147</v>
+        <v>11.0352986320931</v>
       </c>
     </row>
     <row r="623">
@@ -30274,7 +30274,7 @@
         <v>803</v>
       </c>
       <c r="B623" t="n">
-        <v>17.3118468086688</v>
+        <v>17.3570221404399</v>
       </c>
     </row>
     <row r="624">
@@ -30282,7 +30282,7 @@
         <v>804</v>
       </c>
       <c r="B624" t="n">
-        <v>21.4341197074796</v>
+        <v>21.3635322419539</v>
       </c>
     </row>
     <row r="625">
@@ -30290,7 +30290,7 @@
         <v>805</v>
       </c>
       <c r="B625" t="n">
-        <v>23.3323223353075</v>
+        <v>23.3797931718392</v>
       </c>
     </row>
     <row r="626">
@@ -30298,7 +30298,7 @@
         <v>806</v>
       </c>
       <c r="B626" t="n">
-        <v>25.4009186238475</v>
+        <v>25.4537969265979</v>
       </c>
     </row>
     <row r="627">
@@ -30306,7 +30306,7 @@
         <v>807</v>
       </c>
       <c r="B627" t="n">
-        <v>27.0789207492012</v>
+        <v>27.1780353421059</v>
       </c>
     </row>
     <row r="628">
@@ -30314,7 +30314,7 @@
         <v>808</v>
       </c>
       <c r="B628" t="n">
-        <v>24.2064002519115</v>
+        <v>24.5520891950694</v>
       </c>
     </row>
     <row r="629">
@@ -30322,7 +30322,7 @@
         <v>809</v>
       </c>
       <c r="B629" t="n">
-        <v>18.830744258507</v>
+        <v>18.4563286964188</v>
       </c>
     </row>
     <row r="630">
@@ -30330,7 +30330,7 @@
         <v>810</v>
       </c>
       <c r="B630" t="n">
-        <v>14.8761161920464</v>
+        <v>14.9143581254583</v>
       </c>
     </row>
     <row r="631">
@@ -30338,7 +30338,7 @@
         <v>811</v>
       </c>
       <c r="B631" t="n">
-        <v>11.8041530494256</v>
+        <v>11.6769074983475</v>
       </c>
     </row>
     <row r="632">
@@ -30346,7 +30346,7 @@
         <v>812</v>
       </c>
       <c r="B632" t="n">
-        <v>10.3573415759596</v>
+        <v>10.2014270302325</v>
       </c>
     </row>
     <row r="633">
@@ -30354,7 +30354,7 @@
         <v>813</v>
       </c>
       <c r="B633" t="n">
-        <v>9.24847770496667</v>
+        <v>9.13417916746047</v>
       </c>
     </row>
     <row r="634">
@@ -30362,7 +30362,7 @@
         <v>814</v>
       </c>
       <c r="B634" t="n">
-        <v>8.16585076928013</v>
+        <v>7.91057910356393</v>
       </c>
     </row>
     <row r="635">
@@ -30370,7 +30370,7 @@
         <v>815</v>
       </c>
       <c r="B635" t="n">
-        <v>8.35311985351881</v>
+        <v>8.71374138223431</v>
       </c>
     </row>
     <row r="636">
@@ -30378,7 +30378,7 @@
         <v>816</v>
       </c>
       <c r="B636" t="n">
-        <v>9.35373567249406</v>
+        <v>9.30931842399314</v>
       </c>
     </row>
     <row r="637">
@@ -30386,7 +30386,7 @@
         <v>817</v>
       </c>
       <c r="B637" t="n">
-        <v>9.52847167963953</v>
+        <v>9.55728774659724</v>
       </c>
     </row>
     <row r="638">
@@ -30394,7 +30394,7 @@
         <v>818</v>
       </c>
       <c r="B638" t="n">
-        <v>10.1057338794371</v>
+        <v>10.2699276736572</v>
       </c>
     </row>
     <row r="639">
@@ -30402,7 +30402,7 @@
         <v>819</v>
       </c>
       <c r="B639" t="n">
-        <v>9.74231456782645</v>
+        <v>9.95076410241623</v>
       </c>
     </row>
     <row r="640">
@@ -30410,7 +30410,7 @@
         <v>820</v>
       </c>
       <c r="B640" t="n">
-        <v>9.10655116387751</v>
+        <v>9.36404279467786</v>
       </c>
     </row>
     <row r="641">
@@ -30418,7 +30418,7 @@
         <v>821</v>
       </c>
       <c r="B641" t="n">
-        <v>7.10363950547572</v>
+        <v>6.62904316779314</v>
       </c>
     </row>
     <row r="642">
@@ -30426,7 +30426,7 @@
         <v>822</v>
       </c>
       <c r="B642" t="n">
-        <v>6.24255685499886</v>
+        <v>6.48632593655972</v>
       </c>
     </row>
     <row r="643">
@@ -30434,7 +30434,7 @@
         <v>823</v>
       </c>
       <c r="B643" t="n">
-        <v>5.83516692208002</v>
+        <v>5.86831030736363</v>
       </c>
     </row>
     <row r="644">
@@ -30442,7 +30442,7 @@
         <v>824</v>
       </c>
       <c r="B644" t="n">
-        <v>4.97552334268216</v>
+        <v>4.84028698945146</v>
       </c>
     </row>
     <row r="645">
@@ -30450,7 +30450,7 @@
         <v>825</v>
       </c>
       <c r="B645" t="n">
-        <v>4.65227654662322</v>
+        <v>4.47097022567251</v>
       </c>
     </row>
     <row r="646">
@@ -30458,7 +30458,7 @@
         <v>826</v>
       </c>
       <c r="B646" t="n">
-        <v>5.13579081649996</v>
+        <v>4.91530375126075</v>
       </c>
     </row>
     <row r="647">
@@ -30466,7 +30466,7 @@
         <v>827</v>
       </c>
       <c r="B647" t="n">
-        <v>5.05910351921776</v>
+        <v>5.59020250461025</v>
       </c>
     </row>
     <row r="648">
@@ -30474,7 +30474,7 @@
         <v>828</v>
       </c>
       <c r="B648" t="n">
-        <v>4.7751219896072</v>
+        <v>4.63495069217423</v>
       </c>
     </row>
     <row r="649">
@@ -30482,7 +30482,7 @@
         <v>829</v>
       </c>
       <c r="B649" t="n">
-        <v>5.06145242629722</v>
+        <v>4.97085923087823</v>
       </c>
     </row>
     <row r="650">
@@ -30490,7 +30490,7 @@
         <v>830</v>
       </c>
       <c r="B650" t="n">
-        <v>4.54389626343278</v>
+        <v>4.70683945720762</v>
       </c>
     </row>
     <row r="651">
@@ -30498,7 +30498,7 @@
         <v>831</v>
       </c>
       <c r="B651" t="n">
-        <v>3.16452891786293</v>
+        <v>3.49065407108487</v>
       </c>
     </row>
     <row r="652">
@@ -30506,7 +30506,7 @@
         <v>832</v>
       </c>
       <c r="B652" t="n">
-        <v>3.8425070188742</v>
+        <v>4.22898660683993</v>
       </c>
     </row>
     <row r="653">
@@ -30514,7 +30514,7 @@
         <v>833</v>
       </c>
       <c r="B653" t="n">
-        <v>3.6689772505061</v>
+        <v>3.12169101651319</v>
       </c>
     </row>
     <row r="654">
@@ -30522,7 +30522,7 @@
         <v>834</v>
       </c>
       <c r="B654" t="n">
-        <v>2.89349037465196</v>
+        <v>3.00518746317494</v>
       </c>
     </row>
     <row r="655">
@@ -30530,7 +30530,7 @@
         <v>835</v>
       </c>
       <c r="B655" t="n">
-        <v>3.13481439460129</v>
+        <v>3.30231678017797</v>
       </c>
     </row>
     <row r="656">
@@ -30538,7 +30538,7 @@
         <v>836</v>
       </c>
       <c r="B656" t="n">
-        <v>4.01671144486509</v>
+        <v>3.91268486330936</v>
       </c>
     </row>
     <row r="657">
@@ -30546,7 +30546,7 @@
         <v>837</v>
       </c>
       <c r="B657" t="n">
-        <v>4.98741004765708</v>
+        <v>4.66159557275232</v>
       </c>
     </row>
     <row r="658">
@@ -30554,7 +30554,7 @@
         <v>838</v>
       </c>
       <c r="B658" t="n">
-        <v>3.78429545313242</v>
+        <v>3.37688052620531</v>
       </c>
     </row>
     <row r="659">
@@ -30562,7 +30562,7 @@
         <v>839</v>
       </c>
       <c r="B659" t="n">
-        <v>4.08258649894524</v>
+        <v>4.56582918323637</v>
       </c>
     </row>
     <row r="660">
@@ -30570,7 +30570,7 @@
         <v>840</v>
       </c>
       <c r="B660" t="n">
-        <v>3.88284275866723</v>
+        <v>3.83094523215118</v>
       </c>
     </row>
     <row r="661">
@@ -30578,7 +30578,7 @@
         <v>841</v>
       </c>
       <c r="B661" t="n">
-        <v>2.82334116099639</v>
+        <v>2.66057774716916</v>
       </c>
     </row>
     <row r="662">
@@ -30586,7 +30586,7 @@
         <v>842</v>
       </c>
       <c r="B662" t="n">
-        <v>2.57802478811753</v>
+        <v>2.75684281480171</v>
       </c>
     </row>
     <row r="663">
@@ -30594,7 +30594,7 @@
         <v>843</v>
       </c>
       <c r="B663" t="n">
-        <v>3.08431755461937</v>
+        <v>3.47206900850163</v>
       </c>
     </row>
     <row r="664">
@@ -30602,7 +30602,7 @@
         <v>844</v>
       </c>
       <c r="B664" t="n">
-        <v>3.91086056613048</v>
+        <v>4.49302785528737</v>
       </c>
     </row>
     <row r="665">
@@ -30610,7 +30610,7 @@
         <v>845</v>
       </c>
       <c r="B665" t="n">
-        <v>4.75249136410995</v>
+        <v>4.28512320015062</v>
       </c>
     </row>
     <row r="666">
@@ -30618,7 +30618,7 @@
         <v>846</v>
       </c>
       <c r="B666" t="n">
-        <v>6.04513424639247</v>
+        <v>6.00937726123868</v>
       </c>
     </row>
     <row r="667">
@@ -30626,7 +30626,7 @@
         <v>847</v>
       </c>
       <c r="B667" t="n">
-        <v>6.16421341785958</v>
+        <v>6.32487180196061</v>
       </c>
     </row>
     <row r="668">
@@ -30634,7 +30634,7 @@
         <v>848</v>
       </c>
       <c r="B668" t="n">
-        <v>5.33845567309256</v>
+        <v>5.22514416598943</v>
       </c>
     </row>
     <row r="669">
@@ -30642,7 +30642,7 @@
         <v>849</v>
       </c>
       <c r="B669" t="n">
-        <v>4.8546723120974</v>
+        <v>4.46968152656183</v>
       </c>
     </row>
     <row r="670">
@@ -30650,7 +30650,7 @@
         <v>850</v>
       </c>
       <c r="B670" t="n">
-        <v>4.47290880119526</v>
+        <v>3.87907144231193</v>
       </c>
     </row>
     <row r="671">
@@ -30658,7 +30658,7 @@
         <v>851</v>
       </c>
       <c r="B671" t="n">
-        <v>3.95844135444012</v>
+        <v>4.62162840999782</v>
       </c>
     </row>
     <row r="672">
@@ -30666,7 +30666,7 @@
         <v>852</v>
       </c>
       <c r="B672" t="n">
-        <v>4.43098323410537</v>
+        <v>4.40136213693314</v>
       </c>
     </row>
     <row r="673">
@@ -30674,7 +30674,7 @@
         <v>853</v>
       </c>
       <c r="B673" t="n">
-        <v>5.74610979375672</v>
+        <v>5.52262612027832</v>
       </c>
     </row>
     <row r="674">
@@ -30682,7 +30682,7 @@
         <v>854</v>
       </c>
       <c r="B674" t="n">
-        <v>6.15180678582497</v>
+        <v>6.44341808448336</v>
       </c>
     </row>
     <row r="675">
@@ -30690,7 +30690,7 @@
         <v>855</v>
       </c>
       <c r="B675" t="n">
-        <v>6.00190399972491</v>
+        <v>6.34868686532077</v>
       </c>
     </row>
     <row r="676">
@@ -30698,7 +30698,7 @@
         <v>856</v>
       </c>
       <c r="B676" t="n">
-        <v>5.93500316368342</v>
+        <v>6.51777666639147</v>
       </c>
     </row>
     <row r="677">
@@ -30706,7 +30706,7 @@
         <v>857</v>
       </c>
       <c r="B677" t="n">
-        <v>7.43576696164324</v>
+        <v>6.73794984037638</v>
       </c>
     </row>
     <row r="678">
@@ -30714,7 +30714,7 @@
         <v>858</v>
       </c>
       <c r="B678" t="n">
-        <v>6.27646878366535</v>
+        <v>6.18679393363316</v>
       </c>
     </row>
     <row r="679">
@@ -30722,7 +30722,7 @@
         <v>859</v>
       </c>
       <c r="B679" t="n">
-        <v>5.36113100924909</v>
+        <v>5.5829651881011</v>
       </c>
     </row>
     <row r="680">
@@ -30730,7 +30730,7 @@
         <v>860</v>
       </c>
       <c r="B680" t="n">
-        <v>6.59025228159649</v>
+        <v>6.10782472284694</v>
       </c>
     </row>
     <row r="681">
@@ -30738,7 +30738,7 @@
         <v>861</v>
       </c>
       <c r="B681" t="n">
-        <v>7.04803096713889</v>
+        <v>6.60106602424382</v>
       </c>
     </row>
     <row r="682">
@@ -30746,7 +30746,7 @@
         <v>862</v>
       </c>
       <c r="B682" t="n">
-        <v>7.07891650026064</v>
+        <v>6.42559386997612</v>
       </c>
     </row>
     <row r="683">
@@ -30754,7 +30754,7 @@
         <v>863</v>
       </c>
       <c r="B683" t="n">
-        <v>5.43907585767737</v>
+        <v>6.02743290105358</v>
       </c>
     </row>
     <row r="684">
@@ -30762,7 +30762,7 @@
         <v>864</v>
       </c>
       <c r="B684" t="n">
-        <v>5.78642790739566</v>
+        <v>5.80170129165989</v>
       </c>
     </row>
     <row r="685">
@@ -30770,7 +30770,7 @@
         <v>865</v>
       </c>
       <c r="B685" t="n">
-        <v>5.39889813604741</v>
+        <v>5.13660362678391</v>
       </c>
     </row>
     <row r="686">
@@ -30778,7 +30778,7 @@
         <v>866</v>
       </c>
       <c r="B686" t="n">
-        <v>3.56512295329451</v>
+        <v>3.99221565570889</v>
       </c>
     </row>
     <row r="687">
@@ -30786,7 +30786,7 @@
         <v>867</v>
       </c>
       <c r="B687" t="n">
-        <v>3.8000849937736</v>
+        <v>4.14616600165909</v>
       </c>
     </row>
     <row r="688">
@@ -30794,7 +30794,7 @@
         <v>868</v>
       </c>
       <c r="B688" t="n">
-        <v>3.25874915787752</v>
+        <v>4.02307750477146</v>
       </c>
     </row>
     <row r="689">
@@ -30802,7 +30802,7 @@
         <v>869</v>
       </c>
       <c r="B689" t="n">
-        <v>4.99322235650287</v>
+        <v>3.8815984324759</v>
       </c>
     </row>
     <row r="690">
@@ -30810,7 +30810,7 @@
         <v>870</v>
       </c>
       <c r="B690" t="n">
-        <v>4.62644635954783</v>
+        <v>4.02934051521336</v>
       </c>
     </row>
     <row r="691">
@@ -30818,7 +30818,15 @@
         <v>871</v>
       </c>
       <c r="B691" t="n">
-        <v>4.14048381861414</v>
+        <v>4.36385456028933</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="s">
+        <v>872</v>
+      </c>
+      <c r="B692" t="n">
+        <v>4.02336710576734</v>
       </c>
     </row>
   </sheetData>
@@ -37150,7 +37158,7 @@
         <v>1066</v>
       </c>
       <c r="B790" t="n">
-        <v>2.21</v>
+        <v>2.22941176470588</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -37158,7 +37158,7 @@
         <v>1066</v>
       </c>
       <c r="B790" t="n">
-        <v>2.22941176470588</v>
+        <v>2.24590909090909</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="1068">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -3221,6 +3221,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2026</t>
   </si>
 </sst>
 </file>
@@ -37161,6 +37164,14 @@
         <v>2.24590909090909</v>
       </c>
     </row>
+    <row r="791">
+      <c r="A791" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B791" t="n">
+        <v>2.2875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -2644,6 +2644,9 @@
     <t xml:space="preserve">Feb 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Mar 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">UnempRate</t>
   </si>
   <si>
@@ -3218,9 +3221,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 1968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Apr 2026</t>
@@ -18822,6 +18822,14 @@
         <v>21037.3</v>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" t="s">
+        <v>874</v>
+      </c>
+      <c r="B604" t="n">
+        <v>21051.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18839,7 +18847,7 @@
         <v>262</v>
       </c>
       <c r="B1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2">
@@ -23655,6 +23663,14 @@
         <v>873</v>
       </c>
       <c r="B603" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="s">
+        <v>874</v>
+      </c>
+      <c r="B604" t="n">
         <v>6.7</v>
       </c>
     </row>
@@ -23675,7 +23691,7 @@
         <v>262</v>
       </c>
       <c r="B1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="2">
@@ -25280,7 +25296,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B202"/>
     </row>
@@ -25301,12 +25317,12 @@
         <v>262</v>
       </c>
       <c r="B1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B2" t="n">
         <v>12.9667760753128</v>
@@ -25314,7 +25330,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B3" t="n">
         <v>15.0136942094219</v>
@@ -25322,7 +25338,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B4" t="n">
         <v>15.7173673795166</v>
@@ -25330,7 +25346,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B5" t="n">
         <v>15.0083394292738</v>
@@ -25338,7 +25354,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B6" t="n">
         <v>14.1631513522075</v>
@@ -25346,7 +25362,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B7" t="n">
         <v>14.3196627658395</v>
@@ -25354,7 +25370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B8" t="n">
         <v>14.5659126107761</v>
@@ -25362,7 +25378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B9" t="n">
         <v>11.0934019859703</v>
@@ -25370,7 +25386,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B10" t="n">
         <v>11.5193520347377</v>
@@ -25378,7 +25394,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B11" t="n">
         <v>10.3976063805748</v>
@@ -25386,7 +25402,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B12" t="n">
         <v>10.203544223433</v>
@@ -25394,7 +25410,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B13" t="n">
         <v>8.25370377873824</v>
@@ -25402,7 +25418,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B14" t="n">
         <v>6.74941660698323</v>
@@ -25410,7 +25426,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B15" t="n">
         <v>6.99352943674983</v>
@@ -25418,7 +25434,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B16" t="n">
         <v>8.54641293280502</v>
@@ -25426,7 +25442,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B17" t="n">
         <v>8.36923199167487</v>
@@ -25434,7 +25450,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B18" t="n">
         <v>8.27326635899438</v>
@@ -25442,7 +25458,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B19" t="n">
         <v>9.85826112039194</v>
@@ -25450,7 +25466,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B20" t="n">
         <v>9.91121604952369</v>
@@ -25458,7 +25474,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B21" t="n">
         <v>10.5072207560502</v>
@@ -25466,7 +25482,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B22" t="n">
         <v>7.79066458038734</v>
@@ -25474,7 +25490,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B23" t="n">
         <v>10.9032596283834</v>
@@ -25482,7 +25498,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B24" t="n">
         <v>8.19610135662233</v>
@@ -25490,7 +25506,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B25" t="n">
         <v>9.07734774781358</v>
@@ -25498,7 +25514,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B26" t="n">
         <v>8.50235678691241</v>
@@ -25506,7 +25522,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B27" t="n">
         <v>9.00143117812621</v>
@@ -25514,7 +25530,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B28" t="n">
         <v>9.09344352882898</v>
@@ -25522,7 +25538,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B29" t="n">
         <v>8.12556120408371</v>
@@ -25530,7 +25546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B30" t="n">
         <v>10.7444231936402</v>
@@ -25538,7 +25554,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B31" t="n">
         <v>10.0971199004294</v>
@@ -25546,7 +25562,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B32" t="n">
         <v>11.4278274718587</v>
@@ -25554,7 +25570,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B33" t="n">
         <v>12.506561942725</v>
@@ -25562,7 +25578,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B34" t="n">
         <v>14.8525484100527</v>
@@ -25570,7 +25586,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B35" t="n">
         <v>13.9647049646935</v>
@@ -25578,7 +25594,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B36" t="n">
         <v>13.8193035567392</v>
@@ -25586,7 +25602,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B37" t="n">
         <v>14.3299854004434</v>
@@ -25594,7 +25610,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B38" t="n">
         <v>15.3018079241173</v>
@@ -25602,7 +25618,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B39" t="n">
         <v>15.0270385091154</v>
@@ -25610,7 +25626,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B40" t="n">
         <v>13.2518711756956</v>
@@ -25618,7 +25634,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B41" t="n">
         <v>13.1332186179338</v>
@@ -25626,7 +25642,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B42" t="n">
         <v>12.6578401751251</v>
@@ -25634,7 +25650,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B43" t="n">
         <v>11.2954913894953</v>
@@ -25642,7 +25658,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B44" t="n">
         <v>12.7456975920676</v>
@@ -25650,7 +25666,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B45" t="n">
         <v>12.0988566109835</v>
@@ -25658,7 +25674,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B46" t="n">
         <v>12.4954011343489</v>
@@ -25666,7 +25682,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B47" t="n">
         <v>14.2289904200083</v>
@@ -25674,7 +25690,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B48" t="n">
         <v>13.4484012949889</v>
@@ -25682,7 +25698,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B49" t="n">
         <v>15.6988273068042</v>
@@ -25690,7 +25706,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B50" t="n">
         <v>14.2845925451855</v>
@@ -25698,7 +25714,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B51" t="n">
         <v>13.7513624713095</v>
@@ -25706,7 +25722,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B52" t="n">
         <v>16.5561760195999</v>
@@ -25714,7 +25730,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B53" t="n">
         <v>15.9924726433944</v>
@@ -25722,7 +25738,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B54" t="n">
         <v>16.8425831874094</v>
@@ -25730,7 +25746,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B55" t="n">
         <v>16.5276746861153</v>
@@ -25738,7 +25754,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B56" t="n">
         <v>16.4698895002538</v>
@@ -25746,7 +25762,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B57" t="n">
         <v>17.2134250823613</v>
@@ -25754,7 +25770,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B58" t="n">
         <v>15.6816081666631</v>
@@ -25762,7 +25778,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B59" t="n">
         <v>14.8028853950233</v>
@@ -25770,7 +25786,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B60" t="n">
         <v>15.2426482221366</v>
@@ -25778,7 +25794,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B61" t="n">
         <v>15.6902851909184</v>
@@ -25786,7 +25802,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B62" t="n">
         <v>16.5013128950056</v>
@@ -25794,7 +25810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B63" t="n">
         <v>17.144059922985</v>
@@ -25802,7 +25818,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B64" t="n">
         <v>17.3090733250565</v>
@@ -25810,7 +25826,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B65" t="n">
         <v>19.1915260629344</v>
@@ -25818,7 +25834,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B66" t="n">
         <v>22.7683604016704</v>
@@ -25826,7 +25842,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B67" t="n">
         <v>23.3483213053937</v>
@@ -25834,7 +25850,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B68" t="n">
         <v>23.7330017100268</v>
@@ -25842,7 +25858,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B69" t="n">
         <v>24.5746121277929</v>
@@ -25850,7 +25866,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B70" t="n">
         <v>25.299565253288</v>
@@ -25858,7 +25874,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B71" t="n">
         <v>25.0912717707172</v>
@@ -25866,7 +25882,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B72" t="n">
         <v>23.9521568788769</v>
@@ -25874,7 +25890,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B73" t="n">
         <v>21.1869735832747</v>
@@ -25882,7 +25898,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B74" t="n">
         <v>20.6527071997174</v>
@@ -25890,7 +25906,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B75" t="n">
         <v>20.1659943690496</v>
@@ -25898,7 +25914,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B76" t="n">
         <v>18.9358160000968</v>
@@ -25906,7 +25922,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B77" t="n">
         <v>16.9203967093089</v>
@@ -25914,7 +25930,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B78" t="n">
         <v>12.907810848208</v>
@@ -25922,7 +25938,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B79" t="n">
         <v>12.4545658937996</v>
@@ -25930,7 +25946,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B80" t="n">
         <v>13.2184526911685</v>
@@ -25938,7 +25954,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B81" t="n">
         <v>14.2594274489356</v>
@@ -25946,7 +25962,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B82" t="n">
         <v>14.1362614616155</v>
@@ -25954,7 +25970,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B83" t="n">
         <v>17.5108308988957</v>
@@ -25962,7 +25978,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B84" t="n">
         <v>17.8203047316368</v>
@@ -25970,7 +25986,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B85" t="n">
         <v>19.6199365813437</v>
@@ -25978,7 +25994,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B86" t="n">
         <v>18.3178769926645</v>
@@ -25986,7 +26002,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B87" t="n">
         <v>16.4922800191838</v>
@@ -25994,7 +26010,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B88" t="n">
         <v>18.0934981429238</v>
@@ -26002,7 +26018,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B89" t="n">
         <v>14.9717615097796</v>
@@ -26010,7 +26026,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B90" t="n">
         <v>15.137570465284</v>
@@ -26018,7 +26034,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B91" t="n">
         <v>17.0502997395172</v>
@@ -30846,15 +30862,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B2" t="n">
         <v>3.02666666666667</v>
@@ -30862,7 +30878,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B3" t="n">
         <v>2.66</v>
@@ -30870,7 +30886,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B4" t="n">
         <v>1.93285714285714</v>
@@ -30878,7 +30894,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B5" t="n">
         <v>2.59368421052632</v>
@@ -30886,7 +30902,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B6" t="n">
         <v>3.37809523809524</v>
@@ -30894,7 +30910,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B7" t="n">
         <v>3.61809523809524</v>
@@ -30902,7 +30918,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B8" t="n">
         <v>3.19952380952381</v>
@@ -30910,7 +30926,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B9" t="n">
         <v>3.0585</v>
@@ -30918,7 +30934,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B10" t="n">
         <v>3.20818181818182</v>
@@ -30926,7 +30942,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B11" t="n">
         <v>3.27578947368421</v>
@@ -30934,7 +30950,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B12" t="n">
         <v>3.18227272727273</v>
@@ -30942,7 +30958,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B13" t="n">
         <v>2.79714285714286</v>
@@ -30950,7 +30966,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B14" t="n">
         <v>2.6</v>
@@ -30958,7 +30974,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B15" t="n">
         <v>2.4995652173913</v>
@@ -30966,7 +30982,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B16" t="n">
         <v>2.381</v>
@@ -30974,7 +30990,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B17" t="n">
         <v>2.52666666666667</v>
@@ -30982,7 +30998,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B18" t="n">
         <v>2.39909090909091</v>
@@ -30990,7 +31006,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B19" t="n">
         <v>2.73526315789474</v>
@@ -30998,7 +31014,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B20" t="n">
         <v>3.06681818181818</v>
@@ -31006,7 +31022,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B21" t="n">
         <v>3.0855</v>
@@ -31014,7 +31030,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B22" t="n">
         <v>3.10681818181818</v>
@@ -31022,7 +31038,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B23" t="n">
         <v>3.07421052631579</v>
@@ -31030,7 +31046,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B24" t="n">
         <v>3.31772727272727</v>
@@ -31038,7 +31054,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B25" t="n">
         <v>4.24</v>
@@ -31046,7 +31062,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B26" t="n">
         <v>5.3725</v>
@@ -31054,7 +31070,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B27" t="n">
         <v>5.12</v>
@@ -31062,7 +31078,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B28" t="n">
         <v>5.01055555555556</v>
@@ -31070,7 +31086,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B29" t="n">
         <v>4.515</v>
@@ -31078,7 +31094,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B30" t="n">
         <v>3.85909090909091</v>
@@ -31086,7 +31102,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B31" t="n">
         <v>3.835</v>
@@ -31094,7 +31110,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B32" t="n">
         <v>3.83181818181818</v>
@@ -31102,7 +31118,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B33" t="n">
         <v>3.6535</v>
@@ -31110,7 +31126,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B34" t="n">
         <v>3.61904761904762</v>
@@ -31118,7 +31134,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B35" t="n">
         <v>3.5955</v>
@@ -31126,7 +31142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B36" t="n">
         <v>3.37176470588235</v>
@@ -31134,7 +31150,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B37" t="n">
         <v>3.21842105263158</v>
@@ -31142,7 +31158,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B38" t="n">
         <v>3.37227272727273</v>
@@ -31150,7 +31166,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B39" t="n">
         <v>3.60190476190476</v>
@@ -31158,7 +31174,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B40" t="n">
         <v>3.688</v>
@@ -31166,7 +31182,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B41" t="n">
         <v>3.55136363636364</v>
@@ -31174,7 +31190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B42" t="n">
         <v>3.622</v>
@@ -31182,7 +31198,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B43" t="n">
         <v>3.6925</v>
@@ -31190,7 +31206,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B44" t="n">
         <v>3.76</v>
@@ -31198,7 +31214,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B45" t="n">
         <v>3.7965</v>
@@ -31206,7 +31222,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B46" t="n">
         <v>3.8715</v>
@@ -31214,7 +31230,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B47" t="n">
         <v>3.74</v>
@@ -31222,7 +31238,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B48" t="n">
         <v>3.655</v>
@@ -31230,7 +31246,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B49" t="n">
         <v>3.54545454545455</v>
@@ -31238,7 +31254,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B50" t="n">
         <v>3.58952380952381</v>
@@ -31246,7 +31262,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B51" t="n">
         <v>3.78380952380952</v>
@@ -31254,7 +31270,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B52" t="n">
         <v>3.79809523809524</v>
@@ -31262,7 +31278,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B53" t="n">
         <v>3.69761904761905</v>
@@ -31270,7 +31286,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B54" t="n">
         <v>3.72315789473684</v>
@@ -31278,7 +31294,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B55" t="n">
         <v>3.84227272727273</v>
@@ -31286,7 +31302,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B56" t="n">
         <v>3.776</v>
@@ -31294,7 +31310,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B57" t="n">
         <v>3.7135</v>
@@ -31302,7 +31318,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B58" t="n">
         <v>3.7004347826087</v>
@@ -31310,7 +31326,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B59" t="n">
         <v>3.655</v>
@@ -31318,7 +31334,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B60" t="n">
         <v>3.8395</v>
@@ -31326,7 +31342,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B61" t="n">
         <v>3.95363636363636</v>
@@ -31334,7 +31350,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B62" t="n">
         <v>3.98190476190476</v>
@@ -31342,7 +31358,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B63" t="n">
         <v>4.08</v>
@@ -31350,7 +31366,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B64" t="n">
         <v>4.10428571428571</v>
@@ -31358,7 +31374,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B65" t="n">
         <v>4.1465</v>
@@ -31366,7 +31382,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B66" t="n">
         <v>4.17619047619048</v>
@@ -31374,7 +31390,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B67" t="n">
         <v>4.44045454545455</v>
@@ -31382,7 +31398,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B68" t="n">
         <v>4.59526315789474</v>
@@ -31390,7 +31406,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B69" t="n">
         <v>4.658</v>
@@ -31398,7 +31414,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B70" t="n">
         <v>4.84</v>
@@ -31406,7 +31422,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B71" t="n">
         <v>5.077</v>
@@ -31414,7 +31430,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B72" t="n">
         <v>5.08952380952381</v>
@@ -31422,7 +31438,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B73" t="n">
         <v>5.05090909090909</v>
@@ -31430,7 +31446,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B74" t="n">
         <v>5.06052631578947</v>
@@ -31438,7 +31454,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B75" t="n">
         <v>5.05</v>
@@ -31446,7 +31462,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B76" t="n">
         <v>5.01571428571429</v>
@@ -31454,7 +31470,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B77" t="n">
         <v>5.113</v>
@@ -31462,7 +31478,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B78" t="n">
         <v>5.19619047619048</v>
@@ -31470,7 +31486,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B79" t="n">
         <v>5.071</v>
@@ -31478,7 +31494,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B80" t="n">
         <v>4.82904761904762</v>
@@ -31486,7 +31502,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B81" t="n">
         <v>4.595</v>
@@ -31494,7 +31510,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B82" t="n">
         <v>4.27045454545455</v>
@@ -31502,7 +31518,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B83" t="n">
         <v>4.0045</v>
@@ -31510,7 +31526,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B84" t="n">
         <v>4.11954545454545</v>
@@ -31518,7 +31534,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B85" t="n">
         <v>4.33722222222222</v>
@@ -31526,7 +31542,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B86" t="n">
         <v>4.273</v>
@@ -31534,7 +31550,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B87" t="n">
         <v>4.32952380952381</v>
@@ -31542,7 +31558,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B88" t="n">
         <v>4.475</v>
@@ -31550,7 +31566,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B89" t="n">
         <v>4.90857142857143</v>
@@ -31558,7 +31574,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B90" t="n">
         <v>5.13904761904762</v>
@@ -31566,7 +31582,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B91" t="n">
         <v>5.753</v>
@@ -31574,7 +31590,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B92" t="n">
         <v>5.99181818181818</v>
@@ -31582,7 +31598,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B93" t="n">
         <v>6.60666666666667</v>
@@ -31590,7 +31606,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B94" t="n">
         <v>6.92285714285714</v>
@@ -31598,7 +31614,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B95" t="n">
         <v>6.91142857142857</v>
@@ -31606,7 +31622,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B96" t="n">
         <v>6.94714285714286</v>
@@ -31614,7 +31630,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B97" t="n">
         <v>6.7675</v>
@@ -31622,7 +31638,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B98" t="n">
         <v>6.23157894736842</v>
@@ -31630,7 +31646,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B99" t="n">
         <v>5.8</v>
@@ -31638,7 +31654,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B100" t="n">
         <v>5.59</v>
@@ -31646,7 +31662,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B101" t="n">
         <v>5.62636363636364</v>
@@ -31654,7 +31670,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B102" t="n">
         <v>5.6305</v>
@@ -31662,7 +31678,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B103" t="n">
         <v>5.898</v>
@@ -31670,7 +31686,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B104" t="n">
         <v>6.38272727272727</v>
@@ -31678,7 +31694,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B105" t="n">
         <v>6.28842105263158</v>
@@ -31686,7 +31702,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B106" t="n">
         <v>6.60571428571429</v>
@@ -31694,7 +31710,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B107" t="n">
         <v>6.67333333333333</v>
@@ -31702,7 +31718,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B108" t="n">
         <v>6.74571428571429</v>
@@ -31710,7 +31726,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B109" t="n">
         <v>6.9905</v>
@@ -31718,7 +31734,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B110" t="n">
         <v>7.44210526315789</v>
@@ -31726,7 +31742,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B111" t="n">
         <v>7.62666666666667</v>
@@ -31734,7 +31750,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B112" t="n">
         <v>7.73761904761905</v>
@@ -31742,7 +31758,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B113" t="n">
         <v>7.68363636363636</v>
@@ -31750,7 +31766,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B114" t="n">
         <v>7.69</v>
@@ -31758,7 +31774,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B115" t="n">
         <v>7.77117647058823</v>
@@ -31766,7 +31782,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B116" t="n">
         <v>7.80666666666667</v>
@@ -31774,7 +31790,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B117" t="n">
         <v>7.718125</v>
@@ -31782,7 +31798,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B118" t="n">
         <v>7.38857142857143</v>
@@ -31790,7 +31806,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B119" t="n">
         <v>6.80947368421053</v>
@@ -31798,7 +31814,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B120" t="n">
         <v>6.57315789473684</v>
@@ -31806,7 +31822,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B121" t="n">
         <v>5.92904761904762</v>
@@ -31814,7 +31830,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B122" t="n">
         <v>5.76611111111111</v>
@@ -31822,7 +31838,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B123" t="n">
         <v>5.676</v>
@@ -31830,7 +31846,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B124" t="n">
         <v>5.46285714285714</v>
@@ -31838,7 +31854,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B125" t="n">
         <v>5.30380952380952</v>
@@ -31846,7 +31862,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B126" t="n">
         <v>4.821875</v>
@@ -31854,7 +31870,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B127" t="n">
         <v>4.46105263157895</v>
@@ -31862,7 +31878,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B128" t="n">
         <v>4.583</v>
@@ -31870,7 +31886,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B129" t="n">
         <v>4.62421052631579</v>
@@ -31878,7 +31894,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B130" t="n">
         <v>3.36818181818182</v>
@@ -31886,7 +31902,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B131" t="n">
         <v>3.07333333333333</v>
@@ -31894,7 +31910,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B132" t="n">
         <v>3.0535</v>
@@ -31902,7 +31918,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B133" t="n">
         <v>3.10954545454545</v>
@@ -31910,7 +31926,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B134" t="n">
         <v>3.54142857142857</v>
@@ -31918,7 +31934,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B135" t="n">
         <v>3.87136363636364</v>
@@ -31926,7 +31942,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B136" t="n">
         <v>3.89666666666667</v>
@@ -31934,7 +31950,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B137" t="n">
         <v>3.848</v>
@@ -31942,7 +31958,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B138" t="n">
         <v>3.33285714285714</v>
@@ -31950,7 +31966,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B139" t="n">
         <v>3.24636363636364</v>
@@ -31958,7 +31974,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B140" t="n">
         <v>3.281</v>
@@ -31966,7 +31982,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B141" t="n">
         <v>3.47789473684211</v>
@@ -31974,7 +31990,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B142" t="n">
         <v>3.4952380952381</v>
@@ -31982,7 +31998,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B143" t="n">
         <v>3.64052631578947</v>
@@ -31990,7 +32006,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B144" t="n">
         <v>3.66952380952381</v>
@@ -31998,7 +32014,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B145" t="n">
         <v>3.61590909090909</v>
@@ -32006,7 +32022,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B146" t="n">
         <v>3.4875</v>
@@ -32014,7 +32030,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B147" t="n">
         <v>3.46</v>
@@ -32022,7 +32038,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B148" t="n">
         <v>3.5605</v>
@@ -32030,7 +32046,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B149" t="n">
         <v>3.56857142857143</v>
@@ -32038,7 +32054,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B150" t="n">
         <v>3.60571428571429</v>
@@ -32046,7 +32062,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B151" t="n">
         <v>3.67736842105263</v>
@@ -32054,7 +32070,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B152" t="n">
         <v>3.77727272727273</v>
@@ -32062,7 +32078,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B153" t="n">
         <v>3.925</v>
@@ -32070,7 +32086,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B154" t="n">
         <v>4.25636363636364</v>
@@ -32078,7 +32094,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B155" t="n">
         <v>4.71444444444444</v>
@@ -32086,7 +32102,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B156" t="n">
         <v>5.10681818181818</v>
@@ -32094,7 +32110,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B157" t="n">
         <v>5.35666666666667</v>
@@ -32102,7 +32118,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B158" t="n">
         <v>5.65285714285714</v>
@@ -32110,7 +32126,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B159" t="n">
         <v>6.01136363636364</v>
@@ -32118,7 +32134,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B160" t="n">
         <v>6.38105263157895</v>
@@ -32126,7 +32142,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B161" t="n">
         <v>6.48545454545455</v>
@@ -32134,7 +32150,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B162" t="n">
         <v>6.45952380952381</v>
@@ -32142,7 +32158,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B163" t="n">
         <v>6.38263157894737</v>
@@ -32150,7 +32166,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B164" t="n">
         <v>6.29090909090909</v>
@@ -32158,7 +32174,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B165" t="n">
         <v>6.1445</v>
@@ -32166,7 +32182,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B166" t="n">
         <v>6.25</v>
@@ -32174,7 +32190,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B167" t="n">
         <v>7.23571428571429</v>
@@ -32182,7 +32198,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B168" t="n">
         <v>8.28</v>
@@ -32190,7 +32206,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B169" t="n">
         <v>8.6555</v>
@@ -32198,7 +32214,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B170" t="n">
         <v>8.87954545454545</v>
@@ -32206,7 +32222,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B171" t="n">
         <v>9.09666666666667</v>
@@ -32214,7 +32230,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B172" t="n">
         <v>9.026</v>
@@ -32222,7 +32238,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B173" t="n">
         <v>8.63681818181818</v>
@@ -32230,7 +32246,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B174" t="n">
         <v>7.827</v>
@@ -32238,7 +32254,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B175" t="n">
         <v>7.3205</v>
@@ -32246,7 +32262,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B176" t="n">
         <v>6.65090909090909</v>
@@ -32254,7 +32270,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B177" t="n">
         <v>6.351</v>
@@ -32262,7 +32278,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B178" t="n">
         <v>6.277</v>
@@ -32270,7 +32286,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B179" t="n">
         <v>6.49181818181818</v>
@@ -32278,7 +32294,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B180" t="n">
         <v>6.92142857142857</v>
@@ -32286,7 +32302,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B181" t="n">
         <v>6.95285714285714</v>
@@ -32294,7 +32310,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B182" t="n">
         <v>7.22409090909091</v>
@@ -32302,7 +32318,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B183" t="n">
         <v>7.71125</v>
@@ -32310,7 +32326,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B184" t="n">
         <v>8.38380952380952</v>
@@ -32318,7 +32334,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B185" t="n">
         <v>8.32136363636364</v>
@@ -32326,7 +32342,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B186" t="n">
         <v>8.42105263157895</v>
@@ -32334,7 +32350,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B187" t="n">
         <v>8.55809523809524</v>
@@ -37158,7 +37174,7 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1066</v>
+        <v>874</v>
       </c>
       <c r="B790" t="n">
         <v>2.24590909090909</v>
@@ -37169,7 +37185,7 @@
         <v>1067</v>
       </c>
       <c r="B791" t="n">
-        <v>2.2875</v>
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -30845,7 +30845,15 @@
         <v>872</v>
       </c>
       <c r="B692" t="n">
-        <v>4.02336710576734</v>
+        <v>4.16927880169948</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="s">
+        <v>873</v>
+      </c>
+      <c r="B693" t="n">
+        <v>3.59736348663501</v>
       </c>
     </row>
   </sheetData>
@@ -37185,7 +37193,7 @@
         <v>1067</v>
       </c>
       <c r="B791" t="n">
-        <v>2.27</v>
+        <v>2.26571428571429</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="1069">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -3224,6 +3224,9 @@
   </si>
   <si>
     <t xml:space="preserve">Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 2026</t>
   </si>
 </sst>
 </file>
@@ -37193,7 +37196,15 @@
         <v>1067</v>
       </c>
       <c r="B791" t="n">
-        <v>2.26571428571429</v>
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B792" t="n">
+        <v>2.29</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -30749,7 +30749,7 @@
         <v>849</v>
       </c>
       <c r="B668" t="n">
-        <v>5.22514416598943</v>
+        <v>5.20814692429619</v>
       </c>
     </row>
     <row r="669">
@@ -30757,7 +30757,7 @@
         <v>850</v>
       </c>
       <c r="B669" t="n">
-        <v>4.46968152656183</v>
+        <v>4.43643458493724</v>
       </c>
     </row>
     <row r="670">
@@ -30765,7 +30765,7 @@
         <v>851</v>
       </c>
       <c r="B670" t="n">
-        <v>3.87907144231193</v>
+        <v>3.82852011648303</v>
       </c>
     </row>
     <row r="671">
@@ -30773,7 +30773,7 @@
         <v>852</v>
       </c>
       <c r="B671" t="n">
-        <v>4.62162840999782</v>
+        <v>4.57099888619846</v>
       </c>
     </row>
     <row r="672">
@@ -30781,7 +30781,7 @@
         <v>853</v>
       </c>
       <c r="B672" t="n">
-        <v>4.40136213693314</v>
+        <v>4.35084148405768</v>
       </c>
     </row>
     <row r="673">
@@ -30789,7 +30789,7 @@
         <v>854</v>
       </c>
       <c r="B673" t="n">
-        <v>5.52262612027832</v>
+        <v>5.47223314279404</v>
       </c>
     </row>
     <row r="674">
@@ -30797,7 +30797,7 @@
         <v>855</v>
       </c>
       <c r="B674" t="n">
-        <v>6.44341808448336</v>
+        <v>6.41013784488794</v>
       </c>
     </row>
     <row r="675">
@@ -30805,7 +30805,7 @@
         <v>856</v>
       </c>
       <c r="B675" t="n">
-        <v>6.34868686532077</v>
+        <v>6.33172107126688</v>
       </c>
     </row>
     <row r="676">
@@ -30813,7 +30813,7 @@
         <v>857</v>
       </c>
       <c r="B676" t="n">
-        <v>6.51777666639147</v>
+        <v>6.51834044955629</v>
       </c>
     </row>
     <row r="677">
@@ -30821,7 +30821,7 @@
         <v>858</v>
       </c>
       <c r="B677" t="n">
-        <v>6.73794984037638</v>
+        <v>6.73910668131498</v>
       </c>
     </row>
     <row r="678">
@@ -30829,7 +30829,7 @@
         <v>859</v>
       </c>
       <c r="B678" t="n">
-        <v>6.18679393363316</v>
+        <v>6.18827296964122</v>
       </c>
     </row>
     <row r="679">
@@ -30837,7 +30837,7 @@
         <v>860</v>
       </c>
       <c r="B679" t="n">
-        <v>5.5829651881011</v>
+        <v>5.58429509750073</v>
       </c>
     </row>
     <row r="680">
@@ -30845,7 +30845,7 @@
         <v>861</v>
       </c>
       <c r="B680" t="n">
-        <v>6.10782472284694</v>
+        <v>6.10974674518887</v>
       </c>
     </row>
     <row r="681">
@@ -30853,7 +30853,7 @@
         <v>862</v>
       </c>
       <c r="B681" t="n">
-        <v>6.60106602424382</v>
+        <v>6.60271918872614</v>
       </c>
     </row>
     <row r="682">
@@ -30861,7 +30861,7 @@
         <v>863</v>
       </c>
       <c r="B682" t="n">
-        <v>6.42559386997612</v>
+        <v>6.42688175654435</v>
       </c>
     </row>
     <row r="683">
@@ -30869,7 +30869,7 @@
         <v>864</v>
       </c>
       <c r="B683" t="n">
-        <v>6.02743290105358</v>
+        <v>6.02917181563913</v>
       </c>
     </row>
     <row r="684">
@@ -30877,7 +30877,7 @@
         <v>865</v>
       </c>
       <c r="B684" t="n">
-        <v>5.80170129165989</v>
+        <v>5.80374444730647</v>
       </c>
     </row>
     <row r="685">
@@ -30885,7 +30885,7 @@
         <v>866</v>
       </c>
       <c r="B685" t="n">
-        <v>5.13660362678391</v>
+        <v>5.13934779897651</v>
       </c>
     </row>
     <row r="686">
@@ -30893,7 +30893,7 @@
         <v>867</v>
       </c>
       <c r="B686" t="n">
-        <v>3.99221565570889</v>
+        <v>3.99543378532705</v>
       </c>
     </row>
     <row r="687">
@@ -30901,7 +30901,7 @@
         <v>868</v>
       </c>
       <c r="B687" t="n">
-        <v>4.14616600165909</v>
+        <v>4.15106011934001</v>
       </c>
     </row>
     <row r="688">
@@ -30909,7 +30909,7 @@
         <v>869</v>
       </c>
       <c r="B688" t="n">
-        <v>4.02307750477146</v>
+        <v>4.02928417787216</v>
       </c>
     </row>
     <row r="689">
@@ -30917,7 +30917,7 @@
         <v>870</v>
       </c>
       <c r="B689" t="n">
-        <v>3.8815984324759</v>
+        <v>3.85246443943114</v>
       </c>
     </row>
     <row r="690">
@@ -30925,7 +30925,7 @@
         <v>871</v>
       </c>
       <c r="B690" t="n">
-        <v>4.02934051521336</v>
+        <v>3.96590181275134</v>
       </c>
     </row>
     <row r="691">
@@ -30933,7 +30933,7 @@
         <v>872</v>
       </c>
       <c r="B691" t="n">
-        <v>4.35729304790229</v>
+        <v>4.25927041857146</v>
       </c>
     </row>
     <row r="692">
@@ -30941,7 +30941,7 @@
         <v>873</v>
       </c>
       <c r="B692" t="n">
-        <v>4.16053719969073</v>
+        <v>3.96183245282122</v>
       </c>
     </row>
     <row r="693">
@@ -30949,7 +30949,7 @@
         <v>874</v>
       </c>
       <c r="B693" t="n">
-        <v>3.58079931289037</v>
+        <v>3.28494971979241</v>
       </c>
     </row>
     <row r="694">
@@ -30957,7 +30957,15 @@
         <v>875</v>
       </c>
       <c r="B694" t="n">
-        <v>3.69288630372422</v>
+        <v>3.26227555145181</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="s">
+        <v>876</v>
+      </c>
+      <c r="B695" t="n">
+        <v>3.11529760672831</v>
       </c>
     </row>
   </sheetData>
@@ -37313,7 +37321,7 @@
         <v>1070</v>
       </c>
       <c r="B793" t="n">
-        <v>2.29333333333333</v>
+        <v>2.26952380952381</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="1072">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -3233,6 +3233,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -37321,7 +37324,15 @@
         <v>1070</v>
       </c>
       <c r="B793" t="n">
-        <v>2.26952380952381</v>
+        <v>2.26909090909091</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B794" t="n">
+        <v>2.2575</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -2656,6 +2656,9 @@
     <t xml:space="preserve">May 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Jun 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">UnempRate</t>
   </si>
   <si>
@@ -3230,9 +3233,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 1968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jun 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Jul 2026</t>
@@ -18905,6 +18905,14 @@
         <v>21121.5</v>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" t="s">
+        <v>878</v>
+      </c>
+      <c r="B607" t="n">
+        <v>21139.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18922,7 +18930,7 @@
         <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="2">
@@ -23763,6 +23771,14 @@
       </c>
       <c r="B606" t="n">
         <v>6.6</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="s">
+        <v>878</v>
+      </c>
+      <c r="B607" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -23782,7 +23798,7 @@
         <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="2">
@@ -25395,7 +25411,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B203"/>
     </row>
@@ -25416,12 +25432,12 @@
         <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B2" t="n">
         <v>12.9667760753128</v>
@@ -25429,7 +25445,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B3" t="n">
         <v>15.0136942094219</v>
@@ -25437,7 +25453,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B4" t="n">
         <v>15.7173673795166</v>
@@ -25445,7 +25461,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B5" t="n">
         <v>15.0083394292738</v>
@@ -25453,7 +25469,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B6" t="n">
         <v>14.1631513522075</v>
@@ -25461,7 +25477,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B7" t="n">
         <v>14.3196627658395</v>
@@ -25469,7 +25485,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B8" t="n">
         <v>14.5659126107761</v>
@@ -25477,7 +25493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B9" t="n">
         <v>11.0934019859703</v>
@@ -25485,7 +25501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B10" t="n">
         <v>11.5193520347377</v>
@@ -25493,7 +25509,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B11" t="n">
         <v>10.3976063805748</v>
@@ -25501,7 +25517,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B12" t="n">
         <v>10.203544223433</v>
@@ -25509,7 +25525,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B13" t="n">
         <v>8.25370377873824</v>
@@ -25517,7 +25533,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B14" t="n">
         <v>6.74941660698323</v>
@@ -25525,7 +25541,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B15" t="n">
         <v>6.99352943674983</v>
@@ -25533,7 +25549,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B16" t="n">
         <v>8.54641293280502</v>
@@ -25541,7 +25557,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B17" t="n">
         <v>8.36923199167487</v>
@@ -25549,7 +25565,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B18" t="n">
         <v>8.27326635899438</v>
@@ -25557,7 +25573,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B19" t="n">
         <v>9.85826112039194</v>
@@ -25565,7 +25581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B20" t="n">
         <v>9.91121604952369</v>
@@ -25573,7 +25589,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B21" t="n">
         <v>10.5072207560502</v>
@@ -25581,7 +25597,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B22" t="n">
         <v>7.79066458038734</v>
@@ -25589,7 +25605,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B23" t="n">
         <v>10.9032596283834</v>
@@ -25597,7 +25613,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B24" t="n">
         <v>8.19610135662233</v>
@@ -25605,7 +25621,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B25" t="n">
         <v>9.07734774781358</v>
@@ -25613,7 +25629,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B26" t="n">
         <v>8.50235678691241</v>
@@ -25621,7 +25637,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B27" t="n">
         <v>9.00143117812621</v>
@@ -25629,7 +25645,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B28" t="n">
         <v>9.09344352882898</v>
@@ -25637,7 +25653,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B29" t="n">
         <v>8.12556120408371</v>
@@ -25645,7 +25661,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B30" t="n">
         <v>10.7444231936402</v>
@@ -25653,7 +25669,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B31" t="n">
         <v>10.0971199004294</v>
@@ -25661,7 +25677,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B32" t="n">
         <v>11.4278274718587</v>
@@ -25669,7 +25685,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B33" t="n">
         <v>12.506561942725</v>
@@ -25677,7 +25693,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B34" t="n">
         <v>14.8525484100527</v>
@@ -25685,7 +25701,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B35" t="n">
         <v>13.9647049646935</v>
@@ -25693,7 +25709,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B36" t="n">
         <v>13.8193035567392</v>
@@ -25701,7 +25717,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B37" t="n">
         <v>14.3299854004434</v>
@@ -25709,7 +25725,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B38" t="n">
         <v>15.3018079241173</v>
@@ -25717,7 +25733,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B39" t="n">
         <v>15.0270385091154</v>
@@ -25725,7 +25741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B40" t="n">
         <v>13.2518711756956</v>
@@ -25733,7 +25749,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B41" t="n">
         <v>13.1332186179338</v>
@@ -25741,7 +25757,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B42" t="n">
         <v>12.6578401751251</v>
@@ -25749,7 +25765,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B43" t="n">
         <v>11.2954913894953</v>
@@ -25757,7 +25773,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B44" t="n">
         <v>12.7456975920676</v>
@@ -25765,7 +25781,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B45" t="n">
         <v>12.0988566109835</v>
@@ -25773,7 +25789,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B46" t="n">
         <v>12.4954011343489</v>
@@ -25781,7 +25797,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B47" t="n">
         <v>14.2289904200083</v>
@@ -25789,7 +25805,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B48" t="n">
         <v>13.4484012949889</v>
@@ -25797,7 +25813,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B49" t="n">
         <v>15.6988273068042</v>
@@ -25805,7 +25821,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B50" t="n">
         <v>14.2845925451855</v>
@@ -25813,7 +25829,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B51" t="n">
         <v>13.7513624713095</v>
@@ -25821,7 +25837,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B52" t="n">
         <v>16.5561760195999</v>
@@ -25829,7 +25845,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B53" t="n">
         <v>15.9924726433944</v>
@@ -25837,7 +25853,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B54" t="n">
         <v>16.8425831874094</v>
@@ -25845,7 +25861,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B55" t="n">
         <v>16.5276746861153</v>
@@ -25853,7 +25869,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B56" t="n">
         <v>16.4698895002538</v>
@@ -25861,7 +25877,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B57" t="n">
         <v>17.2134250823613</v>
@@ -25869,7 +25885,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B58" t="n">
         <v>15.6816081666631</v>
@@ -25877,7 +25893,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B59" t="n">
         <v>14.8028853950233</v>
@@ -25885,7 +25901,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B60" t="n">
         <v>15.2426482221366</v>
@@ -25893,7 +25909,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B61" t="n">
         <v>15.6902851909184</v>
@@ -25901,7 +25917,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B62" t="n">
         <v>16.5013128950056</v>
@@ -25909,7 +25925,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B63" t="n">
         <v>17.144059922985</v>
@@ -25917,7 +25933,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B64" t="n">
         <v>17.3090733250565</v>
@@ -25925,7 +25941,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B65" t="n">
         <v>19.1915260629344</v>
@@ -25933,7 +25949,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B66" t="n">
         <v>22.7683604016704</v>
@@ -25941,7 +25957,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B67" t="n">
         <v>23.3483213053937</v>
@@ -25949,7 +25965,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B68" t="n">
         <v>23.7330017100268</v>
@@ -25957,7 +25973,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B69" t="n">
         <v>24.5746121277929</v>
@@ -25965,7 +25981,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B70" t="n">
         <v>25.299565253288</v>
@@ -25973,7 +25989,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B71" t="n">
         <v>25.0912717707172</v>
@@ -25981,7 +25997,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B72" t="n">
         <v>23.9521568788769</v>
@@ -25989,7 +26005,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B73" t="n">
         <v>21.1869735832747</v>
@@ -25997,7 +26013,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B74" t="n">
         <v>20.6527071997174</v>
@@ -26005,7 +26021,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B75" t="n">
         <v>20.1659943690496</v>
@@ -26013,7 +26029,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B76" t="n">
         <v>18.9358160000968</v>
@@ -26021,7 +26037,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B77" t="n">
         <v>16.9203967093089</v>
@@ -26029,7 +26045,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B78" t="n">
         <v>12.907810848208</v>
@@ -26037,7 +26053,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B79" t="n">
         <v>12.4545658937996</v>
@@ -26045,7 +26061,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B80" t="n">
         <v>13.2184526911685</v>
@@ -26053,7 +26069,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B81" t="n">
         <v>14.2594274489356</v>
@@ -26061,7 +26077,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B82" t="n">
         <v>14.1362614616155</v>
@@ -26069,7 +26085,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B83" t="n">
         <v>17.5108308988957</v>
@@ -26077,7 +26093,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B84" t="n">
         <v>17.8203047316368</v>
@@ -26085,7 +26101,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B85" t="n">
         <v>19.6199365813437</v>
@@ -26093,7 +26109,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B86" t="n">
         <v>18.3178769926645</v>
@@ -26101,7 +26117,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B87" t="n">
         <v>16.4922800191838</v>
@@ -26109,7 +26125,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B88" t="n">
         <v>18.0934981429238</v>
@@ -26117,7 +26133,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B89" t="n">
         <v>14.9717615097796</v>
@@ -26125,7 +26141,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B90" t="n">
         <v>15.137570465284</v>
@@ -26133,7 +26149,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B91" t="n">
         <v>17.0502997395172</v>
@@ -30985,15 +31001,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B2" t="n">
         <v>3.02666666666667</v>
@@ -31001,7 +31017,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B3" t="n">
         <v>2.66</v>
@@ -31009,7 +31025,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B4" t="n">
         <v>1.93285714285714</v>
@@ -31017,7 +31033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B5" t="n">
         <v>2.59368421052632</v>
@@ -31025,7 +31041,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B6" t="n">
         <v>3.37809523809524</v>
@@ -31033,7 +31049,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B7" t="n">
         <v>3.61809523809524</v>
@@ -31041,7 +31057,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B8" t="n">
         <v>3.19952380952381</v>
@@ -31049,7 +31065,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B9" t="n">
         <v>3.0585</v>
@@ -31057,7 +31073,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B10" t="n">
         <v>3.20818181818182</v>
@@ -31065,7 +31081,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B11" t="n">
         <v>3.27578947368421</v>
@@ -31073,7 +31089,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B12" t="n">
         <v>3.18227272727273</v>
@@ -31081,7 +31097,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B13" t="n">
         <v>2.79714285714286</v>
@@ -31089,7 +31105,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B14" t="n">
         <v>2.6</v>
@@ -31097,7 +31113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B15" t="n">
         <v>2.4995652173913</v>
@@ -31105,7 +31121,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B16" t="n">
         <v>2.381</v>
@@ -31113,7 +31129,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B17" t="n">
         <v>2.52666666666667</v>
@@ -31121,7 +31137,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B18" t="n">
         <v>2.39909090909091</v>
@@ -31129,7 +31145,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B19" t="n">
         <v>2.73526315789474</v>
@@ -31137,7 +31153,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B20" t="n">
         <v>3.06681818181818</v>
@@ -31145,7 +31161,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B21" t="n">
         <v>3.0855</v>
@@ -31153,7 +31169,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B22" t="n">
         <v>3.10681818181818</v>
@@ -31161,7 +31177,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B23" t="n">
         <v>3.07421052631579</v>
@@ -31169,7 +31185,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B24" t="n">
         <v>3.31772727272727</v>
@@ -31177,7 +31193,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B25" t="n">
         <v>4.24</v>
@@ -31185,7 +31201,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B26" t="n">
         <v>5.3725</v>
@@ -31193,7 +31209,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B27" t="n">
         <v>5.12</v>
@@ -31201,7 +31217,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B28" t="n">
         <v>5.01055555555556</v>
@@ -31209,7 +31225,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B29" t="n">
         <v>4.515</v>
@@ -31217,7 +31233,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B30" t="n">
         <v>3.85909090909091</v>
@@ -31225,7 +31241,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B31" t="n">
         <v>3.835</v>
@@ -31233,7 +31249,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B32" t="n">
         <v>3.83181818181818</v>
@@ -31241,7 +31257,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B33" t="n">
         <v>3.6535</v>
@@ -31249,7 +31265,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B34" t="n">
         <v>3.61904761904762</v>
@@ -31257,7 +31273,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B35" t="n">
         <v>3.5955</v>
@@ -31265,7 +31281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B36" t="n">
         <v>3.37176470588235</v>
@@ -31273,7 +31289,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B37" t="n">
         <v>3.21842105263158</v>
@@ -31281,7 +31297,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B38" t="n">
         <v>3.37227272727273</v>
@@ -31289,7 +31305,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B39" t="n">
         <v>3.60190476190476</v>
@@ -31297,7 +31313,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B40" t="n">
         <v>3.688</v>
@@ -31305,7 +31321,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B41" t="n">
         <v>3.55136363636364</v>
@@ -31313,7 +31329,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B42" t="n">
         <v>3.622</v>
@@ -31321,7 +31337,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B43" t="n">
         <v>3.6925</v>
@@ -31329,7 +31345,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B44" t="n">
         <v>3.76</v>
@@ -31337,7 +31353,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B45" t="n">
         <v>3.7965</v>
@@ -31345,7 +31361,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B46" t="n">
         <v>3.8715</v>
@@ -31353,7 +31369,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B47" t="n">
         <v>3.74</v>
@@ -31361,7 +31377,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B48" t="n">
         <v>3.655</v>
@@ -31369,7 +31385,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B49" t="n">
         <v>3.54545454545455</v>
@@ -31377,7 +31393,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B50" t="n">
         <v>3.58952380952381</v>
@@ -31385,7 +31401,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B51" t="n">
         <v>3.78380952380952</v>
@@ -31393,7 +31409,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B52" t="n">
         <v>3.79809523809524</v>
@@ -31401,7 +31417,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B53" t="n">
         <v>3.69761904761905</v>
@@ -31409,7 +31425,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B54" t="n">
         <v>3.72315789473684</v>
@@ -31417,7 +31433,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B55" t="n">
         <v>3.84227272727273</v>
@@ -31425,7 +31441,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B56" t="n">
         <v>3.776</v>
@@ -31433,7 +31449,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B57" t="n">
         <v>3.7135</v>
@@ -31441,7 +31457,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B58" t="n">
         <v>3.7004347826087</v>
@@ -31449,7 +31465,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B59" t="n">
         <v>3.655</v>
@@ -31457,7 +31473,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B60" t="n">
         <v>3.8395</v>
@@ -31465,7 +31481,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B61" t="n">
         <v>3.95363636363636</v>
@@ -31473,7 +31489,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B62" t="n">
         <v>3.98190476190476</v>
@@ -31481,7 +31497,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B63" t="n">
         <v>4.08</v>
@@ -31489,7 +31505,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B64" t="n">
         <v>4.10428571428571</v>
@@ -31497,7 +31513,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B65" t="n">
         <v>4.1465</v>
@@ -31505,7 +31521,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B66" t="n">
         <v>4.17619047619048</v>
@@ -31513,7 +31529,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B67" t="n">
         <v>4.44045454545455</v>
@@ -31521,7 +31537,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B68" t="n">
         <v>4.59526315789474</v>
@@ -31529,7 +31545,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B69" t="n">
         <v>4.658</v>
@@ -31537,7 +31553,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B70" t="n">
         <v>4.84</v>
@@ -31545,7 +31561,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B71" t="n">
         <v>5.077</v>
@@ -31553,7 +31569,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B72" t="n">
         <v>5.08952380952381</v>
@@ -31561,7 +31577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B73" t="n">
         <v>5.05090909090909</v>
@@ -31569,7 +31585,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B74" t="n">
         <v>5.06052631578947</v>
@@ -31577,7 +31593,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B75" t="n">
         <v>5.05</v>
@@ -31585,7 +31601,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B76" t="n">
         <v>5.01571428571429</v>
@@ -31593,7 +31609,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B77" t="n">
         <v>5.113</v>
@@ -31601,7 +31617,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B78" t="n">
         <v>5.19619047619048</v>
@@ -31609,7 +31625,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B79" t="n">
         <v>5.071</v>
@@ -31617,7 +31633,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B80" t="n">
         <v>4.82904761904762</v>
@@ -31625,7 +31641,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B81" t="n">
         <v>4.595</v>
@@ -31633,7 +31649,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B82" t="n">
         <v>4.27045454545455</v>
@@ -31641,7 +31657,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B83" t="n">
         <v>4.0045</v>
@@ -31649,7 +31665,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B84" t="n">
         <v>4.11954545454545</v>
@@ -31657,7 +31673,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B85" t="n">
         <v>4.33722222222222</v>
@@ -31665,7 +31681,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B86" t="n">
         <v>4.273</v>
@@ -31673,7 +31689,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B87" t="n">
         <v>4.32952380952381</v>
@@ -31681,7 +31697,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B88" t="n">
         <v>4.475</v>
@@ -31689,7 +31705,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B89" t="n">
         <v>4.90857142857143</v>
@@ -31697,7 +31713,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B90" t="n">
         <v>5.13904761904762</v>
@@ -31705,7 +31721,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B91" t="n">
         <v>5.753</v>
@@ -31713,7 +31729,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B92" t="n">
         <v>5.99181818181818</v>
@@ -31721,7 +31737,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B93" t="n">
         <v>6.60666666666667</v>
@@ -31729,7 +31745,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B94" t="n">
         <v>6.92285714285714</v>
@@ -31737,7 +31753,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B95" t="n">
         <v>6.91142857142857</v>
@@ -31745,7 +31761,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B96" t="n">
         <v>6.94714285714286</v>
@@ -31753,7 +31769,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B97" t="n">
         <v>6.7675</v>
@@ -31761,7 +31777,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B98" t="n">
         <v>6.23157894736842</v>
@@ -31769,7 +31785,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B99" t="n">
         <v>5.8</v>
@@ -31777,7 +31793,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B100" t="n">
         <v>5.59</v>
@@ -31785,7 +31801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B101" t="n">
         <v>5.62636363636364</v>
@@ -31793,7 +31809,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B102" t="n">
         <v>5.6305</v>
@@ -31801,7 +31817,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B103" t="n">
         <v>5.898</v>
@@ -31809,7 +31825,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B104" t="n">
         <v>6.38272727272727</v>
@@ -31817,7 +31833,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B105" t="n">
         <v>6.28842105263158</v>
@@ -31825,7 +31841,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B106" t="n">
         <v>6.60571428571429</v>
@@ -31833,7 +31849,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B107" t="n">
         <v>6.67333333333333</v>
@@ -31841,7 +31857,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B108" t="n">
         <v>6.74571428571429</v>
@@ -31849,7 +31865,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B109" t="n">
         <v>6.9905</v>
@@ -31857,7 +31873,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B110" t="n">
         <v>7.44210526315789</v>
@@ -31865,7 +31881,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B111" t="n">
         <v>7.62666666666667</v>
@@ -31873,7 +31889,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B112" t="n">
         <v>7.73761904761905</v>
@@ -31881,7 +31897,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B113" t="n">
         <v>7.68363636363636</v>
@@ -31889,7 +31905,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B114" t="n">
         <v>7.69</v>
@@ -31897,7 +31913,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B115" t="n">
         <v>7.77117647058823</v>
@@ -31905,7 +31921,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B116" t="n">
         <v>7.80666666666667</v>
@@ -31913,7 +31929,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B117" t="n">
         <v>7.718125</v>
@@ -31921,7 +31937,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B118" t="n">
         <v>7.38857142857143</v>
@@ -31929,7 +31945,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B119" t="n">
         <v>6.80947368421053</v>
@@ -31937,7 +31953,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B120" t="n">
         <v>6.57315789473684</v>
@@ -31945,7 +31961,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B121" t="n">
         <v>5.92904761904762</v>
@@ -31953,7 +31969,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B122" t="n">
         <v>5.76611111111111</v>
@@ -31961,7 +31977,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B123" t="n">
         <v>5.676</v>
@@ -31969,7 +31985,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B124" t="n">
         <v>5.46285714285714</v>
@@ -31977,7 +31993,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B125" t="n">
         <v>5.30380952380952</v>
@@ -31985,7 +32001,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B126" t="n">
         <v>4.821875</v>
@@ -31993,7 +32009,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B127" t="n">
         <v>4.46105263157895</v>
@@ -32001,7 +32017,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B128" t="n">
         <v>4.583</v>
@@ -32009,7 +32025,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B129" t="n">
         <v>4.62421052631579</v>
@@ -32017,7 +32033,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B130" t="n">
         <v>3.36818181818182</v>
@@ -32025,7 +32041,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B131" t="n">
         <v>3.07333333333333</v>
@@ -32033,7 +32049,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B132" t="n">
         <v>3.0535</v>
@@ -32041,7 +32057,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B133" t="n">
         <v>3.10954545454545</v>
@@ -32049,7 +32065,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B134" t="n">
         <v>3.54142857142857</v>
@@ -32057,7 +32073,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B135" t="n">
         <v>3.87136363636364</v>
@@ -32065,7 +32081,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B136" t="n">
         <v>3.89666666666667</v>
@@ -32073,7 +32089,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B137" t="n">
         <v>3.848</v>
@@ -32081,7 +32097,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B138" t="n">
         <v>3.33285714285714</v>
@@ -32089,7 +32105,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B139" t="n">
         <v>3.24636363636364</v>
@@ -32097,7 +32113,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B140" t="n">
         <v>3.281</v>
@@ -32105,7 +32121,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B141" t="n">
         <v>3.47789473684211</v>
@@ -32113,7 +32129,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B142" t="n">
         <v>3.4952380952381</v>
@@ -32121,7 +32137,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B143" t="n">
         <v>3.64052631578947</v>
@@ -32129,7 +32145,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B144" t="n">
         <v>3.66952380952381</v>
@@ -32137,7 +32153,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B145" t="n">
         <v>3.61590909090909</v>
@@ -32145,7 +32161,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B146" t="n">
         <v>3.4875</v>
@@ -32153,7 +32169,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B147" t="n">
         <v>3.46</v>
@@ -32161,7 +32177,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B148" t="n">
         <v>3.5605</v>
@@ -32169,7 +32185,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B149" t="n">
         <v>3.56857142857143</v>
@@ -32177,7 +32193,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B150" t="n">
         <v>3.60571428571429</v>
@@ -32185,7 +32201,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B151" t="n">
         <v>3.67736842105263</v>
@@ -32193,7 +32209,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B152" t="n">
         <v>3.77727272727273</v>
@@ -32201,7 +32217,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B153" t="n">
         <v>3.925</v>
@@ -32209,7 +32225,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B154" t="n">
         <v>4.25636363636364</v>
@@ -32217,7 +32233,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B155" t="n">
         <v>4.71444444444444</v>
@@ -32225,7 +32241,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B156" t="n">
         <v>5.10681818181818</v>
@@ -32233,7 +32249,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B157" t="n">
         <v>5.35666666666667</v>
@@ -32241,7 +32257,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B158" t="n">
         <v>5.65285714285714</v>
@@ -32249,7 +32265,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B159" t="n">
         <v>6.01136363636364</v>
@@ -32257,7 +32273,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B160" t="n">
         <v>6.38105263157895</v>
@@ -32265,7 +32281,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B161" t="n">
         <v>6.48545454545455</v>
@@ -32273,7 +32289,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B162" t="n">
         <v>6.45952380952381</v>
@@ -32281,7 +32297,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B163" t="n">
         <v>6.38263157894737</v>
@@ -32289,7 +32305,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B164" t="n">
         <v>6.29090909090909</v>
@@ -32297,7 +32313,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B165" t="n">
         <v>6.1445</v>
@@ -32305,7 +32321,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B166" t="n">
         <v>6.25</v>
@@ -32313,7 +32329,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B167" t="n">
         <v>7.23571428571429</v>
@@ -32321,7 +32337,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B168" t="n">
         <v>8.28</v>
@@ -32329,7 +32345,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B169" t="n">
         <v>8.6555</v>
@@ -32337,7 +32353,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B170" t="n">
         <v>8.87954545454545</v>
@@ -32345,7 +32361,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B171" t="n">
         <v>9.09666666666667</v>
@@ -32353,7 +32369,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B172" t="n">
         <v>9.026</v>
@@ -32361,7 +32377,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B173" t="n">
         <v>8.63681818181818</v>
@@ -32369,7 +32385,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B174" t="n">
         <v>7.827</v>
@@ -32377,7 +32393,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B175" t="n">
         <v>7.3205</v>
@@ -32385,7 +32401,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B176" t="n">
         <v>6.65090909090909</v>
@@ -32393,7 +32409,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B177" t="n">
         <v>6.351</v>
@@ -32401,7 +32417,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B178" t="n">
         <v>6.277</v>
@@ -32409,7 +32425,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B179" t="n">
         <v>6.49181818181818</v>
@@ -32417,7 +32433,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B180" t="n">
         <v>6.92142857142857</v>
@@ -32425,7 +32441,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B181" t="n">
         <v>6.95285714285714</v>
@@ -32433,7 +32449,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B182" t="n">
         <v>7.22409090909091</v>
@@ -32441,7 +32457,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B183" t="n">
         <v>7.71125</v>
@@ -32449,7 +32465,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B184" t="n">
         <v>8.38380952380952</v>
@@ -32457,7 +32473,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B185" t="n">
         <v>8.32136363636364</v>
@@ -32465,7 +32481,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B186" t="n">
         <v>8.42105263157895</v>
@@ -32473,7 +32489,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B187" t="n">
         <v>8.55809523809524</v>
@@ -37321,7 +37337,7 @@
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1070</v>
+        <v>878</v>
       </c>
       <c r="B793" t="n">
         <v>2.26909090909091</v>
@@ -37332,7 +37348,7 @@
         <v>1071</v>
       </c>
       <c r="B794" t="n">
-        <v>2.2575</v>
+        <v>2.2525</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -30952,7 +30952,7 @@
         <v>872</v>
       </c>
       <c r="B691" t="n">
-        <v>4.25927041857146</v>
+        <v>4.25945242145825</v>
       </c>
     </row>
     <row r="692">
@@ -30960,7 +30960,7 @@
         <v>873</v>
       </c>
       <c r="B692" t="n">
-        <v>3.96183245282122</v>
+        <v>3.96183803700372</v>
       </c>
     </row>
     <row r="693">
@@ -30968,7 +30968,7 @@
         <v>874</v>
       </c>
       <c r="B693" t="n">
-        <v>3.28494971979241</v>
+        <v>3.28495530397491</v>
       </c>
     </row>
     <row r="694">
@@ -30976,7 +30976,7 @@
         <v>875</v>
       </c>
       <c r="B694" t="n">
-        <v>3.26227555145181</v>
+        <v>3.26228113563431</v>
       </c>
     </row>
     <row r="695">
@@ -30984,7 +30984,15 @@
         <v>876</v>
       </c>
       <c r="B695" t="n">
-        <v>3.11529760672831</v>
+        <v>3.7862858229753</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="s">
+        <v>877</v>
+      </c>
+      <c r="B696" t="n">
+        <v>3.73352052169642</v>
       </c>
     </row>
   </sheetData>
@@ -37348,7 +37356,7 @@
         <v>1071</v>
       </c>
       <c r="B794" t="n">
-        <v>2.2525</v>
+        <v>2.25357142857143</v>
       </c>
     </row>
   </sheetData>
